--- a/Hospital Rooms List_R4.xlsx
+++ b/Hospital Rooms List_R4.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="899" uniqueCount="387">
   <si>
     <t>Floor Plan Room Name</t>
   </si>
@@ -56,9 +56,6 @@
   </si>
   <si>
     <t>Room Tag in Japanese</t>
-  </si>
-  <si>
-    <t>Room Tag in English</t>
   </si>
   <si>
     <t>Domain Remarks</t>
@@ -1151,12 +1148,6 @@
     <t>レストラン厨房</t>
   </si>
   <si>
-    <t>Room Name in Japanese</t>
-  </si>
-  <si>
-    <t>Room Name in English</t>
-  </si>
-  <si>
     <t>Clinic Floor</t>
   </si>
   <si>
@@ -1203,6 +1194,12 @@
   </si>
   <si>
     <t>same passage will be use for guard room and Nursery</t>
+  </si>
+  <si>
+    <t>RGB Color code</t>
+  </si>
+  <si>
+    <t>Room Tag in En+E2:F76glish</t>
   </si>
 </sst>
 </file>
@@ -1422,7 +1419,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="43">
+  <borders count="40">
     <border>
       <left/>
       <right/>
@@ -1740,36 +1737,6 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
       <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
@@ -1794,21 +1761,6 @@
       </right>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1974,7 +1926,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="165">
+  <cellXfs count="160">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2127,12 +2079,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2184,9 +2130,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2221,7 +2164,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2230,7 +2173,7 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2239,20 +2182,20 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -2285,26 +2228,26 @@
     <xf numFmtId="0" fontId="8" fillId="12" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="12" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2332,28 +2275,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2368,7 +2308,7 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2377,7 +2317,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2392,7 +2332,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2410,10 +2350,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2428,11 +2368,8 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2670,7 +2607,7 @@
       <xdr:col>13</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:rowOff>106363</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2718,7 +2655,7 @@
       <xdr:col>13</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:rowOff>106363</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2766,7 +2703,7 @@
       <xdr:col>13</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:rowOff>106363</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2814,7 +2751,7 @@
       <xdr:col>13</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:rowOff>106363</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2908,8 +2845,8 @@
     <xdr:to>
       <xdr:col>14</xdr:col>
       <xdr:colOff>55856</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>35662</xdr:rowOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>162662</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2956,7 +2893,7 @@
       <xdr:col>13</xdr:col>
       <xdr:colOff>2243631</xdr:colOff>
       <xdr:row>37</xdr:row>
-      <xdr:rowOff>135307</xdr:rowOff>
+      <xdr:rowOff>95619</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3312,7 +3249,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R234"/>
+  <dimension ref="A1:R233"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="5.375" style="2" bestFit="1" customWidth="1"/>
@@ -3334,1195 +3271,1267 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
-      <c r="A1" s="134" t="s">
+      <c r="A1" s="130" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="135"/>
-      <c r="C1" s="135"/>
-      <c r="D1" s="135"/>
-      <c r="E1" s="135"/>
-      <c r="F1" s="135"/>
-      <c r="G1" s="135"/>
-      <c r="H1" s="135"/>
-      <c r="I1" s="136" t="s">
+      <c r="B1" s="131"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
+      <c r="E1" s="131"/>
+      <c r="F1" s="131"/>
+      <c r="G1" s="131"/>
+      <c r="H1" s="131"/>
+      <c r="I1" s="132" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="137"/>
-      <c r="K1" s="138"/>
+      <c r="J1" s="133"/>
+      <c r="K1" s="134"/>
     </row>
     <row r="2" spans="1:18" s="1" customFormat="1" ht="15">
-      <c r="A2" s="117" t="s">
+      <c r="A2" s="114" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="118" t="s">
+      <c r="B2" s="115" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="118" t="s">
+      <c r="C2" s="115" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="118" t="s">
+      <c r="D2" s="115" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="118" t="s">
+      <c r="E2" s="115" t="s">
+        <v>386</v>
+      </c>
+      <c r="F2" s="115" t="s">
+        <v>385</v>
+      </c>
+      <c r="G2" s="115" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="118"/>
-      <c r="G2" s="118" t="s">
+      <c r="H2" s="116" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="119" t="s">
+      <c r="I2" s="115" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="118" t="s">
+      <c r="J2" s="115" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="118" t="s">
+      <c r="K2" s="115" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="118" t="s">
+      <c r="M2" s="136" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="140" t="s">
+      <c r="N2" s="137"/>
+      <c r="O2" s="138"/>
+      <c r="P2" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="N2" s="141"/>
-      <c r="O2" s="142"/>
-      <c r="P2" s="30" t="s">
+      <c r="Q2" s="3"/>
+    </row>
+    <row r="3" spans="1:18" s="1" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A3" s="87">
+        <v>1</v>
+      </c>
+      <c r="B3" s="151" t="s">
         <v>13</v>
       </c>
-      <c r="Q2" s="3"/>
-    </row>
-    <row r="3" spans="1:18" s="1" customFormat="1" ht="15">
-      <c r="A3" s="90">
-        <v>1</v>
-      </c>
-      <c r="B3" s="155" t="s">
+      <c r="C3" s="139" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="143" t="s">
+      <c r="D3" s="89" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="92" t="s">
+      <c r="E3" s="90" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="91"/>
+      <c r="H3" s="92"/>
+      <c r="I3" s="90" t="s">
+        <v>15</v>
+      </c>
+      <c r="J3" s="90" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="93" t="s">
+      <c r="K3" s="88" t="s">
         <v>16</v>
-      </c>
-      <c r="F3" s="93"/>
-      <c r="G3" s="94"/>
-      <c r="H3" s="95"/>
-      <c r="I3" s="93" t="s">
-        <v>16</v>
-      </c>
-      <c r="J3" s="93" t="s">
-        <v>17</v>
-      </c>
-      <c r="K3" s="91" t="s">
-        <v>17</v>
       </c>
       <c r="M3" s="26"/>
       <c r="N3" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="O3" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="O3" s="28" t="s">
-        <v>19</v>
-      </c>
       <c r="P3" s="29" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Q3" s="4"/>
     </row>
-    <row r="4" spans="1:18" ht="14.25" customHeight="1">
-      <c r="A4" s="96">
+    <row r="4" spans="1:18" ht="14.25" customHeight="1" thickBot="1">
+      <c r="A4" s="93">
         <f t="shared" ref="A4:A10" si="0">A3+1</f>
         <v>2</v>
       </c>
-      <c r="B4" s="153"/>
-      <c r="C4" s="144"/>
+      <c r="B4" s="149"/>
+      <c r="C4" s="140"/>
       <c r="D4" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="51" t="s">
+      <c r="F4" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" s="57"/>
+      <c r="H4" s="94"/>
+      <c r="I4" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="F4" s="133"/>
-      <c r="G4" s="59"/>
-      <c r="H4" s="97"/>
-      <c r="I4" s="51" t="s">
-        <v>22</v>
-      </c>
       <c r="J4" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="K4" s="86" t="s">
         <v>23</v>
-      </c>
-      <c r="K4" s="89" t="s">
-        <v>24</v>
       </c>
       <c r="M4" s="7"/>
       <c r="N4" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="O4" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="O4" s="6" t="s">
+      <c r="P4" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="P4" s="8" t="s">
-        <v>27</v>
-      </c>
       <c r="Q4" s="4"/>
     </row>
-    <row r="5" spans="1:18">
-      <c r="A5" s="96">
+    <row r="5" spans="1:18" ht="15" thickBot="1">
+      <c r="A5" s="93">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="B5" s="153"/>
-      <c r="C5" s="144"/>
+      <c r="B5" s="149"/>
+      <c r="C5" s="140"/>
       <c r="D5" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="51" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="51" t="s">
+      <c r="F5" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" s="57"/>
+      <c r="H5" s="94"/>
+      <c r="I5" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="J5" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="K5" s="86" t="s">
         <v>29</v>
-      </c>
-      <c r="F5" s="133"/>
-      <c r="G5" s="59"/>
-      <c r="H5" s="97"/>
-      <c r="I5" s="51" t="s">
-        <v>28</v>
-      </c>
-      <c r="J5" s="51" t="s">
-        <v>23</v>
-      </c>
-      <c r="K5" s="89" t="s">
-        <v>30</v>
       </c>
       <c r="M5" s="9"/>
       <c r="N5" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="O5" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="O5" s="6" t="s">
+      <c r="P5" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="P5" s="8" t="s">
-        <v>33</v>
-      </c>
       <c r="Q5" s="4"/>
     </row>
-    <row r="6" spans="1:18">
-      <c r="A6" s="96">
+    <row r="6" spans="1:18" ht="15" thickBot="1">
+      <c r="A6" s="93">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B6" s="153"/>
-      <c r="C6" s="144"/>
+      <c r="B6" s="149"/>
+      <c r="C6" s="140"/>
       <c r="D6" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="E6" s="51" t="s">
-        <v>35</v>
-      </c>
-      <c r="F6" s="133"/>
-      <c r="G6" s="59"/>
-      <c r="H6" s="97"/>
+      <c r="F6" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" s="57"/>
+      <c r="H6" s="94"/>
       <c r="I6" s="51" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J6" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="K6" s="86" t="s">
         <v>23</v>
-      </c>
-      <c r="K6" s="89" t="s">
-        <v>24</v>
       </c>
       <c r="M6" s="10"/>
       <c r="N6" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="O6" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="O6" s="6" t="s">
+      <c r="P6" s="8" t="s">
         <v>37</v>
-      </c>
-      <c r="P6" s="8" t="s">
-        <v>38</v>
       </c>
       <c r="Q6" s="5"/>
       <c r="R6" s="5"/>
     </row>
-    <row r="7" spans="1:18">
-      <c r="A7" s="96">
+    <row r="7" spans="1:18" ht="15" thickBot="1">
+      <c r="A7" s="93">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B7" s="153"/>
-      <c r="C7" s="144"/>
+      <c r="B7" s="149"/>
+      <c r="C7" s="140"/>
       <c r="D7" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" s="51" t="s">
         <v>39</v>
       </c>
-      <c r="E7" s="51" t="s">
+      <c r="F7" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" s="57"/>
+      <c r="H7" s="94"/>
+      <c r="I7" s="51" t="s">
         <v>40</v>
       </c>
-      <c r="F7" s="133"/>
-      <c r="G7" s="59"/>
-      <c r="H7" s="97"/>
-      <c r="I7" s="51" t="s">
-        <v>41</v>
-      </c>
       <c r="J7" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="K7" s="86" t="s">
         <v>23</v>
-      </c>
-      <c r="K7" s="89" t="s">
-        <v>24</v>
       </c>
       <c r="M7" s="11"/>
       <c r="N7" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="O7" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="O7" s="6" t="s">
+      <c r="P7" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="P7" s="8" t="s">
-        <v>44</v>
-      </c>
       <c r="Q7" s="4"/>
     </row>
-    <row r="8" spans="1:18" ht="21" customHeight="1">
-      <c r="A8" s="96">
+    <row r="8" spans="1:18" ht="21" customHeight="1" thickBot="1">
+      <c r="A8" s="93">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B8" s="153"/>
-      <c r="C8" s="144"/>
+      <c r="B8" s="149"/>
+      <c r="C8" s="140"/>
       <c r="D8" s="32" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" s="51" t="s">
         <v>45</v>
       </c>
-      <c r="E8" s="51" t="s">
+      <c r="F8" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" s="57"/>
+      <c r="H8" s="94"/>
+      <c r="I8" s="51" t="s">
         <v>46</v>
       </c>
-      <c r="F8" s="133"/>
-      <c r="G8" s="59"/>
-      <c r="H8" s="97"/>
-      <c r="I8" s="51" t="s">
-        <v>47</v>
-      </c>
       <c r="J8" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="K8" s="86" t="s">
         <v>23</v>
-      </c>
-      <c r="K8" s="89" t="s">
-        <v>24</v>
       </c>
       <c r="M8" s="12"/>
       <c r="N8" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="O8" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="O8" s="6" t="s">
-        <v>49</v>
-      </c>
       <c r="P8" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q8" s="4"/>
     </row>
-    <row r="9" spans="1:18">
-      <c r="A9" s="96">
+    <row r="9" spans="1:18" ht="15" thickBot="1">
+      <c r="A9" s="93">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B9" s="153"/>
-      <c r="C9" s="144"/>
+      <c r="B9" s="149"/>
+      <c r="C9" s="140"/>
       <c r="D9" s="31" t="s">
+        <v>49</v>
+      </c>
+      <c r="E9" s="51" t="s">
         <v>50</v>
       </c>
-      <c r="E9" s="51" t="s">
-        <v>51</v>
-      </c>
-      <c r="F9" s="133"/>
-      <c r="G9" s="59"/>
-      <c r="H9" s="97"/>
+      <c r="F9" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" s="57"/>
+      <c r="H9" s="94"/>
       <c r="I9" s="51" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J9" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="K9" s="86" t="s">
         <v>23</v>
-      </c>
-      <c r="K9" s="89" t="s">
-        <v>24</v>
       </c>
       <c r="M9" s="13"/>
       <c r="N9" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="O9" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="O9" s="6" t="s">
-        <v>53</v>
-      </c>
       <c r="P9" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q9" s="4"/>
     </row>
-    <row r="10" spans="1:18">
-      <c r="A10" s="96">
+    <row r="10" spans="1:18" ht="15" thickBot="1">
+      <c r="A10" s="93">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B10" s="153"/>
-      <c r="C10" s="144"/>
+      <c r="B10" s="149"/>
+      <c r="C10" s="140"/>
       <c r="D10" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="E10" s="51" t="s">
         <v>54</v>
       </c>
-      <c r="E10" s="51" t="s">
-        <v>55</v>
-      </c>
-      <c r="F10" s="133"/>
-      <c r="G10" s="59"/>
-      <c r="H10" s="97"/>
+      <c r="F10" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="G10" s="57"/>
+      <c r="H10" s="94"/>
       <c r="I10" s="51" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J10" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="K10" s="86" t="s">
         <v>23</v>
-      </c>
-      <c r="K10" s="89" t="s">
-        <v>24</v>
       </c>
       <c r="M10" s="14"/>
       <c r="N10" s="18" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O10" s="25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P10" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q10" s="4"/>
     </row>
-    <row r="11" spans="1:18">
-      <c r="A11" s="96">
+    <row r="11" spans="1:18" ht="15" thickBot="1">
+      <c r="A11" s="93">
         <f t="shared" ref="A11:A79" si="1">A10+1</f>
         <v>9</v>
       </c>
-      <c r="B11" s="153"/>
-      <c r="C11" s="144" t="s">
+      <c r="B11" s="149"/>
+      <c r="C11" s="140" t="s">
+        <v>56</v>
+      </c>
+      <c r="D11" s="31" t="s">
         <v>57</v>
       </c>
-      <c r="D11" s="31" t="s">
+      <c r="E11" s="51" t="s">
         <v>58</v>
       </c>
-      <c r="E11" s="51" t="s">
+      <c r="F11" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="G11" s="57"/>
+      <c r="H11" s="94"/>
+      <c r="I11" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="J11" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="K11" s="86" t="s">
         <v>59</v>
-      </c>
-      <c r="F11" s="133"/>
-      <c r="G11" s="59"/>
-      <c r="H11" s="97"/>
-      <c r="I11" s="51" t="s">
-        <v>58</v>
-      </c>
-      <c r="J11" s="51" t="s">
-        <v>23</v>
-      </c>
-      <c r="K11" s="89" t="s">
-        <v>60</v>
       </c>
       <c r="M11" s="14"/>
       <c r="N11" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="O11" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="O11" s="6" t="s">
-        <v>62</v>
-      </c>
       <c r="P11" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q11" s="4"/>
     </row>
-    <row r="12" spans="1:18">
-      <c r="A12" s="96">
+    <row r="12" spans="1:18" ht="15" thickBot="1">
+      <c r="A12" s="93">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="B12" s="153"/>
-      <c r="C12" s="144"/>
+      <c r="B12" s="149"/>
+      <c r="C12" s="140"/>
       <c r="D12" s="31" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E12" s="51" t="s">
-        <v>63</v>
-      </c>
-      <c r="F12" s="133"/>
-      <c r="G12" s="59"/>
-      <c r="H12" s="97"/>
+        <v>62</v>
+      </c>
+      <c r="F12" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="G12" s="57"/>
+      <c r="H12" s="94"/>
       <c r="I12" s="51" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J12" s="51" t="s">
-        <v>23</v>
-      </c>
-      <c r="K12" s="89" t="s">
-        <v>60</v>
+        <v>22</v>
+      </c>
+      <c r="K12" s="86" t="s">
+        <v>59</v>
       </c>
       <c r="M12" s="15"/>
       <c r="N12" s="19" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="O12" s="16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P12" s="17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q12" s="4"/>
     </row>
-    <row r="13" spans="1:18" ht="15" customHeight="1">
-      <c r="A13" s="96">
+    <row r="13" spans="1:18" ht="15" customHeight="1" thickBot="1">
+      <c r="A13" s="93">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="B13" s="153"/>
-      <c r="C13" s="144"/>
+      <c r="B13" s="149"/>
+      <c r="C13" s="140"/>
       <c r="D13" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="E13" s="51" t="s">
         <v>65</v>
       </c>
-      <c r="E13" s="51" t="s">
+      <c r="F13" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="G13" s="57"/>
+      <c r="H13" s="94"/>
+      <c r="I13" s="51" t="s">
         <v>66</v>
       </c>
-      <c r="F13" s="133"/>
-      <c r="G13" s="59"/>
-      <c r="H13" s="97"/>
-      <c r="I13" s="51" t="s">
+      <c r="J13" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="J13" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="K13" s="89" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" ht="15" customHeight="1">
-      <c r="A14" s="96">
+      <c r="K13" s="86" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="15" customHeight="1" thickBot="1">
+      <c r="A14" s="93">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="B14" s="153"/>
-      <c r="C14" s="144"/>
+      <c r="B14" s="149"/>
+      <c r="C14" s="140"/>
       <c r="D14" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="E14" s="51" t="s">
         <v>69</v>
       </c>
-      <c r="E14" s="51" t="s">
+      <c r="F14" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="G14" s="57"/>
+      <c r="H14" s="94"/>
+      <c r="I14" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="J14" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="K14" s="86" t="s">
+        <v>23</v>
+      </c>
+      <c r="L14" s="146" t="s">
         <v>70</v>
-      </c>
-      <c r="F14" s="133"/>
-      <c r="G14" s="59"/>
-      <c r="H14" s="97"/>
-      <c r="I14" s="51" t="s">
-        <v>69</v>
-      </c>
-      <c r="J14" s="51" t="s">
-        <v>23</v>
-      </c>
-      <c r="K14" s="89" t="s">
-        <v>24</v>
-      </c>
-      <c r="L14" s="150" t="s">
-        <v>71</v>
       </c>
       <c r="M14" s="5"/>
       <c r="N14" s="21"/>
       <c r="O14" s="5"/>
     </row>
-    <row r="15" spans="1:18" ht="17.25" customHeight="1">
-      <c r="A15" s="96">
+    <row r="15" spans="1:18" ht="17.25" customHeight="1" thickBot="1">
+      <c r="A15" s="93">
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="B15" s="153"/>
-      <c r="C15" s="144"/>
+      <c r="B15" s="149"/>
+      <c r="C15" s="140"/>
       <c r="D15" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="E15" s="51" t="s">
         <v>72</v>
       </c>
-      <c r="E15" s="51" t="s">
+      <c r="F15" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="G15" s="57"/>
+      <c r="H15" s="94"/>
+      <c r="I15" s="51" t="s">
         <v>73</v>
       </c>
-      <c r="F15" s="133"/>
-      <c r="G15" s="59"/>
-      <c r="H15" s="97"/>
-      <c r="I15" s="51" t="s">
-        <v>74</v>
-      </c>
       <c r="J15" s="51" t="s">
-        <v>23</v>
-      </c>
-      <c r="K15" s="89" t="s">
-        <v>60</v>
-      </c>
-      <c r="L15" s="150"/>
-    </row>
-    <row r="16" spans="1:18" ht="17.25" customHeight="1">
-      <c r="A16" s="96">
+        <v>22</v>
+      </c>
+      <c r="K15" s="86" t="s">
+        <v>59</v>
+      </c>
+      <c r="L15" s="146"/>
+    </row>
+    <row r="16" spans="1:18" ht="17.25" customHeight="1" thickBot="1">
+      <c r="A16" s="93">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="B16" s="153"/>
-      <c r="C16" s="144"/>
+      <c r="B16" s="149"/>
+      <c r="C16" s="140"/>
       <c r="D16" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="E16" s="51" t="s">
         <v>69</v>
       </c>
-      <c r="E16" s="51" t="s">
-        <v>70</v>
-      </c>
-      <c r="F16" s="133"/>
-      <c r="G16" s="59"/>
-      <c r="H16" s="97"/>
+      <c r="F16" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="G16" s="57"/>
+      <c r="H16" s="94"/>
       <c r="I16" s="51" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J16" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="K16" s="86" t="s">
         <v>23</v>
       </c>
-      <c r="K16" s="89" t="s">
-        <v>24</v>
-      </c>
-      <c r="L16" s="150"/>
-    </row>
-    <row r="17" spans="1:12" ht="15" customHeight="1">
-      <c r="A17" s="96">
+      <c r="L16" s="146"/>
+    </row>
+    <row r="17" spans="1:12" ht="15" customHeight="1" thickBot="1">
+      <c r="A17" s="93">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="B17" s="153"/>
-      <c r="C17" s="144"/>
+      <c r="B17" s="149"/>
+      <c r="C17" s="140"/>
       <c r="D17" s="31" t="s">
+        <v>74</v>
+      </c>
+      <c r="E17" s="51" t="s">
         <v>75</v>
       </c>
-      <c r="E17" s="51" t="s">
-        <v>76</v>
-      </c>
-      <c r="F17" s="133"/>
-      <c r="G17" s="59"/>
-      <c r="H17" s="97"/>
+      <c r="F17" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="G17" s="57"/>
+      <c r="H17" s="94"/>
       <c r="I17" s="51" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J17" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="K17" s="89" t="s">
-        <v>65</v>
-      </c>
-      <c r="L17" s="150"/>
-    </row>
-    <row r="18" spans="1:12" ht="15" customHeight="1">
-      <c r="A18" s="96">
+        <v>67</v>
+      </c>
+      <c r="K17" s="86" t="s">
+        <v>64</v>
+      </c>
+      <c r="L17" s="146"/>
+    </row>
+    <row r="18" spans="1:12" ht="15" customHeight="1" thickBot="1">
+      <c r="A18" s="93">
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="B18" s="153"/>
-      <c r="C18" s="144"/>
+      <c r="B18" s="149"/>
+      <c r="C18" s="140"/>
       <c r="D18" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="E18" s="51" t="s">
         <v>69</v>
       </c>
-      <c r="E18" s="51" t="s">
-        <v>70</v>
-      </c>
-      <c r="F18" s="133"/>
-      <c r="G18" s="59"/>
-      <c r="H18" s="97"/>
+      <c r="F18" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" s="57"/>
+      <c r="H18" s="94"/>
       <c r="I18" s="51" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J18" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="K18" s="86" t="s">
         <v>23</v>
       </c>
-      <c r="K18" s="89" t="s">
-        <v>24</v>
-      </c>
-      <c r="L18" s="150"/>
+      <c r="L18" s="146"/>
     </row>
     <row r="19" spans="1:12">
-      <c r="A19" s="96">
+      <c r="A19" s="93">
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
-      <c r="B19" s="153"/>
-      <c r="C19" s="144"/>
+      <c r="B19" s="149"/>
+      <c r="C19" s="140"/>
       <c r="D19" s="31" t="s">
+        <v>76</v>
+      </c>
+      <c r="E19" s="51" t="s">
         <v>77</v>
       </c>
-      <c r="E19" s="51" t="s">
-        <v>78</v>
-      </c>
-      <c r="F19" s="133"/>
-      <c r="G19" s="59"/>
-      <c r="H19" s="97"/>
+      <c r="F19" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="G19" s="57"/>
+      <c r="H19" s="94"/>
       <c r="I19" s="51" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J19" s="51" t="s">
-        <v>23</v>
-      </c>
-      <c r="K19" s="89" t="s">
-        <v>60</v>
-      </c>
-      <c r="L19" s="150"/>
+        <v>22</v>
+      </c>
+      <c r="K19" s="86" t="s">
+        <v>59</v>
+      </c>
+      <c r="L19" s="146"/>
     </row>
     <row r="20" spans="1:12">
-      <c r="A20" s="96">
+      <c r="A20" s="93">
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
-      <c r="B20" s="153"/>
-      <c r="C20" s="144"/>
+      <c r="B20" s="149"/>
+      <c r="C20" s="140"/>
       <c r="D20" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="E20" s="51" t="s">
         <v>79</v>
       </c>
-      <c r="E20" s="51" t="s">
+      <c r="F20" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="G20" s="72" t="s">
         <v>80</v>
       </c>
-      <c r="F20" s="133"/>
-      <c r="G20" s="74" t="s">
+      <c r="H20" s="94"/>
+      <c r="I20" s="51" t="s">
+        <v>78</v>
+      </c>
+      <c r="J20" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="K20" s="86" t="s">
         <v>81</v>
       </c>
-      <c r="H20" s="97"/>
-      <c r="I20" s="51" t="s">
-        <v>79</v>
-      </c>
-      <c r="J20" s="51" t="s">
-        <v>23</v>
-      </c>
-      <c r="K20" s="89" t="s">
-        <v>82</v>
-      </c>
-      <c r="L20" s="150"/>
-    </row>
-    <row r="21" spans="1:12">
-      <c r="A21" s="96">
+      <c r="L20" s="146"/>
+    </row>
+    <row r="21" spans="1:12" ht="15" thickBot="1">
+      <c r="A21" s="93">
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
-      <c r="B21" s="153"/>
-      <c r="C21" s="144" t="s">
+      <c r="B21" s="149"/>
+      <c r="C21" s="140" t="s">
+        <v>82</v>
+      </c>
+      <c r="D21" s="34" t="s">
         <v>83</v>
       </c>
-      <c r="D21" s="34" t="s">
+      <c r="E21" s="51" t="s">
         <v>84</v>
       </c>
-      <c r="E21" s="51" t="s">
+      <c r="F21" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G21" s="57"/>
+      <c r="H21" s="94"/>
+      <c r="I21" s="51" t="s">
+        <v>83</v>
+      </c>
+      <c r="J21" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="K21" s="86" t="s">
         <v>85</v>
       </c>
-      <c r="F21" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="G21" s="59"/>
-      <c r="H21" s="97"/>
-      <c r="I21" s="51" t="s">
-        <v>84</v>
-      </c>
-      <c r="J21" s="51" t="s">
-        <v>23</v>
-      </c>
-      <c r="K21" s="89" t="s">
-        <v>86</v>
-      </c>
-      <c r="L21" s="150"/>
-    </row>
-    <row r="22" spans="1:12">
-      <c r="A22" s="96">
+      <c r="L21" s="146"/>
+    </row>
+    <row r="22" spans="1:12" ht="15" thickBot="1">
+      <c r="A22" s="93">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="B22" s="153"/>
-      <c r="C22" s="144"/>
+      <c r="B22" s="149"/>
+      <c r="C22" s="140"/>
       <c r="D22" s="31" t="s">
+        <v>86</v>
+      </c>
+      <c r="E22" s="51" t="s">
         <v>87</v>
       </c>
-      <c r="E22" s="51" t="s">
+      <c r="F22" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="G22" s="57"/>
+      <c r="H22" s="94"/>
+      <c r="I22" s="51" t="s">
+        <v>86</v>
+      </c>
+      <c r="J22" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="K22" s="86" t="s">
         <v>88</v>
       </c>
-      <c r="F22" s="133"/>
-      <c r="G22" s="59"/>
-      <c r="H22" s="97"/>
-      <c r="I22" s="51" t="s">
-        <v>87</v>
-      </c>
-      <c r="J22" s="51" t="s">
-        <v>23</v>
-      </c>
-      <c r="K22" s="89" t="s">
-        <v>89</v>
-      </c>
-      <c r="L22" s="150"/>
-    </row>
-    <row r="23" spans="1:12">
-      <c r="A23" s="96">
+      <c r="L22" s="146"/>
+    </row>
+    <row r="23" spans="1:12" ht="15" thickBot="1">
+      <c r="A23" s="93">
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
-      <c r="B23" s="153"/>
-      <c r="C23" s="144"/>
+      <c r="B23" s="149"/>
+      <c r="C23" s="140"/>
       <c r="D23" s="31" t="s">
+        <v>89</v>
+      </c>
+      <c r="E23" s="51" t="s">
         <v>90</v>
       </c>
-      <c r="E23" s="51" t="s">
+      <c r="F23" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="G23" s="57"/>
+      <c r="H23" s="94"/>
+      <c r="I23" s="51" t="s">
+        <v>89</v>
+      </c>
+      <c r="J23" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="K23" s="86" t="s">
+        <v>23</v>
+      </c>
+      <c r="L23" s="146"/>
+    </row>
+    <row r="24" spans="1:12" ht="15" thickBot="1">
+      <c r="A24" s="93">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B24" s="149"/>
+      <c r="C24" s="140"/>
+      <c r="D24" s="31" t="s">
         <v>91</v>
       </c>
-      <c r="F23" s="133"/>
-      <c r="G23" s="59"/>
-      <c r="H23" s="97"/>
-      <c r="I23" s="51" t="s">
-        <v>90</v>
-      </c>
-      <c r="J23" s="51" t="s">
+      <c r="E24" s="51" t="s">
+        <v>92</v>
+      </c>
+      <c r="F24" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="G24" s="57"/>
+      <c r="H24" s="94"/>
+      <c r="I24" s="51" t="s">
+        <v>91</v>
+      </c>
+      <c r="J24" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="K24" s="86" t="s">
         <v>23</v>
       </c>
-      <c r="K23" s="89" t="s">
-        <v>24</v>
-      </c>
-      <c r="L23" s="150"/>
-    </row>
-    <row r="24" spans="1:12">
-      <c r="A24" s="96">
-        <f t="shared" si="1"/>
-        <v>22</v>
-      </c>
-      <c r="B24" s="153"/>
-      <c r="C24" s="144"/>
-      <c r="D24" s="31" t="s">
-        <v>92</v>
-      </c>
-      <c r="E24" s="51" t="s">
-        <v>93</v>
-      </c>
-      <c r="F24" s="133"/>
-      <c r="G24" s="59"/>
-      <c r="H24" s="97"/>
-      <c r="I24" s="51" t="s">
-        <v>92</v>
-      </c>
-      <c r="J24" s="51" t="s">
-        <v>23</v>
-      </c>
-      <c r="K24" s="89" t="s">
-        <v>24</v>
-      </c>
-      <c r="L24" s="150"/>
-    </row>
-    <row r="25" spans="1:12">
-      <c r="A25" s="96">
+      <c r="L24" s="146"/>
+    </row>
+    <row r="25" spans="1:12" ht="15" thickBot="1">
+      <c r="A25" s="93">
         <f t="shared" si="1"/>
         <v>23</v>
       </c>
-      <c r="B25" s="153"/>
-      <c r="C25" s="144"/>
+      <c r="B25" s="149"/>
+      <c r="C25" s="140"/>
       <c r="D25" s="31" t="s">
+        <v>93</v>
+      </c>
+      <c r="E25" s="51" t="s">
         <v>94</v>
       </c>
-      <c r="E25" s="51" t="s">
-        <v>95</v>
-      </c>
-      <c r="F25" s="133"/>
-      <c r="G25" s="59"/>
-      <c r="H25" s="97"/>
+      <c r="F25" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="G25" s="57"/>
+      <c r="H25" s="94"/>
       <c r="I25" s="51" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J25" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="K25" s="86" t="s">
         <v>23</v>
       </c>
-      <c r="K25" s="89" t="s">
-        <v>24</v>
-      </c>
-      <c r="L25" s="150"/>
-    </row>
-    <row r="26" spans="1:12">
-      <c r="A26" s="96">
+      <c r="L25" s="146"/>
+    </row>
+    <row r="26" spans="1:12" ht="15" thickBot="1">
+      <c r="A26" s="93">
         <f t="shared" si="1"/>
         <v>24</v>
       </c>
-      <c r="B26" s="153"/>
-      <c r="C26" s="145" t="s">
+      <c r="B26" s="149"/>
+      <c r="C26" s="141" t="s">
+        <v>95</v>
+      </c>
+      <c r="D26" s="31" t="s">
         <v>96</v>
       </c>
-      <c r="D26" s="31" t="s">
+      <c r="E26" s="107" t="s">
         <v>97</v>
       </c>
-      <c r="E26" s="110" t="s">
+      <c r="F26" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="G26" s="57"/>
+      <c r="H26" s="94"/>
+      <c r="I26" s="51" t="s">
+        <v>96</v>
+      </c>
+      <c r="J26" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="K26" s="86" t="s">
         <v>98</v>
       </c>
-      <c r="F26" s="110"/>
-      <c r="G26" s="59"/>
-      <c r="H26" s="97"/>
-      <c r="I26" s="51" t="s">
-        <v>97</v>
-      </c>
-      <c r="J26" s="51" t="s">
-        <v>23</v>
-      </c>
-      <c r="K26" s="89" t="s">
-        <v>99</v>
-      </c>
-      <c r="L26" s="150"/>
-    </row>
-    <row r="27" spans="1:12">
-      <c r="A27" s="96">
+      <c r="L26" s="146"/>
+    </row>
+    <row r="27" spans="1:12" ht="15" thickBot="1">
+      <c r="A27" s="93">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="B27" s="153"/>
-      <c r="C27" s="146"/>
-      <c r="D27" s="86" t="s">
+      <c r="B27" s="149"/>
+      <c r="C27" s="142"/>
+      <c r="D27" s="83" t="s">
+        <v>99</v>
+      </c>
+      <c r="E27" s="51" t="s">
         <v>100</v>
       </c>
-      <c r="E27" s="51" t="s">
+      <c r="F27" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="G27" s="118" t="s">
         <v>101</v>
       </c>
-      <c r="F27" s="50"/>
-      <c r="G27" s="121" t="s">
+      <c r="H27" s="94"/>
+      <c r="I27" s="51" t="s">
+        <v>99</v>
+      </c>
+      <c r="J27" s="51" t="s">
         <v>102</v>
       </c>
-      <c r="H27" s="97"/>
-      <c r="I27" s="51" t="s">
-        <v>100</v>
-      </c>
-      <c r="J27" s="51" t="s">
+      <c r="K27" s="86" t="s">
         <v>103</v>
       </c>
-      <c r="K27" s="89" t="s">
-        <v>104</v>
-      </c>
-      <c r="L27" s="150"/>
-    </row>
-    <row r="28" spans="1:12">
-      <c r="A28" s="96">
+      <c r="L27" s="146"/>
+    </row>
+    <row r="28" spans="1:12" ht="15" thickBot="1">
+      <c r="A28" s="93">
         <f t="shared" si="1"/>
         <v>26</v>
       </c>
-      <c r="B28" s="153"/>
-      <c r="C28" s="147"/>
-      <c r="D28" s="86" t="s">
+      <c r="B28" s="149"/>
+      <c r="C28" s="143"/>
+      <c r="D28" s="83" t="s">
+        <v>104</v>
+      </c>
+      <c r="E28" s="51" t="s">
         <v>105</v>
       </c>
-      <c r="E28" s="51" t="s">
+      <c r="F28" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="G28" s="118" t="s">
+        <v>101</v>
+      </c>
+      <c r="H28" s="94"/>
+      <c r="I28" s="51" t="s">
+        <v>104</v>
+      </c>
+      <c r="J28" s="51" t="s">
         <v>106</v>
       </c>
-      <c r="F28" s="50"/>
-      <c r="G28" s="121" t="s">
-        <v>102</v>
-      </c>
-      <c r="H28" s="97"/>
-      <c r="I28" s="51" t="s">
-        <v>105</v>
-      </c>
-      <c r="J28" s="51" t="s">
-        <v>107</v>
-      </c>
-      <c r="K28" s="89" t="s">
-        <v>104</v>
-      </c>
-      <c r="L28" s="150"/>
-    </row>
-    <row r="29" spans="1:12">
-      <c r="A29" s="96">
+      <c r="K28" s="86" t="s">
+        <v>103</v>
+      </c>
+      <c r="L28" s="146"/>
+    </row>
+    <row r="29" spans="1:12" ht="15" thickBot="1">
+      <c r="A29" s="93">
         <f t="shared" si="1"/>
         <v>27</v>
       </c>
-      <c r="B29" s="153"/>
-      <c r="C29" s="144" t="s">
+      <c r="B29" s="149"/>
+      <c r="C29" s="140" t="s">
+        <v>107</v>
+      </c>
+      <c r="D29" s="83" t="s">
         <v>108</v>
       </c>
-      <c r="D29" s="86" t="s">
+      <c r="E29" s="51" t="s">
         <v>109</v>
       </c>
-      <c r="E29" s="51" t="s">
-        <v>110</v>
-      </c>
-      <c r="F29" s="133"/>
-      <c r="G29" s="59"/>
-      <c r="H29" s="97"/>
+      <c r="F29" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="G29" s="57"/>
+      <c r="H29" s="94"/>
       <c r="I29" s="51" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J29" s="51" t="s">
-        <v>23</v>
-      </c>
-      <c r="K29" s="89" t="s">
-        <v>23</v>
-      </c>
-      <c r="L29" s="150"/>
-    </row>
-    <row r="30" spans="1:12">
-      <c r="A30" s="96">
+        <v>22</v>
+      </c>
+      <c r="K29" s="86" t="s">
+        <v>22</v>
+      </c>
+      <c r="L29" s="146"/>
+    </row>
+    <row r="30" spans="1:12" ht="15" thickBot="1">
+      <c r="A30" s="93">
         <f t="shared" si="1"/>
         <v>28</v>
       </c>
-      <c r="B30" s="153"/>
-      <c r="C30" s="144"/>
-      <c r="D30" s="86" t="s">
+      <c r="B30" s="149"/>
+      <c r="C30" s="140"/>
+      <c r="D30" s="83" t="s">
+        <v>110</v>
+      </c>
+      <c r="E30" s="51" t="s">
         <v>111</v>
       </c>
-      <c r="E30" s="51" t="s">
-        <v>112</v>
-      </c>
-      <c r="F30" s="133"/>
-      <c r="G30" s="59"/>
-      <c r="H30" s="97"/>
+      <c r="F30" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="G30" s="57"/>
+      <c r="H30" s="94"/>
       <c r="I30" s="51" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J30" s="51" t="s">
-        <v>23</v>
-      </c>
-      <c r="K30" s="89" t="s">
-        <v>99</v>
-      </c>
-      <c r="L30" s="150"/>
-    </row>
-    <row r="31" spans="1:12">
-      <c r="A31" s="96">
+        <v>22</v>
+      </c>
+      <c r="K30" s="86" t="s">
+        <v>98</v>
+      </c>
+      <c r="L30" s="146"/>
+    </row>
+    <row r="31" spans="1:12" ht="15" thickBot="1">
+      <c r="A31" s="93">
         <f t="shared" si="1"/>
         <v>29</v>
       </c>
-      <c r="B31" s="153"/>
-      <c r="C31" s="144"/>
-      <c r="D31" s="86" t="s">
+      <c r="B31" s="149"/>
+      <c r="C31" s="140"/>
+      <c r="D31" s="83" t="s">
+        <v>112</v>
+      </c>
+      <c r="E31" s="51" t="s">
         <v>113</v>
       </c>
-      <c r="E31" s="51" t="s">
-        <v>114</v>
-      </c>
-      <c r="F31" s="133"/>
-      <c r="G31" s="59"/>
-      <c r="H31" s="97"/>
+      <c r="F31" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="G31" s="57"/>
+      <c r="H31" s="94"/>
       <c r="I31" s="51" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J31" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="K31" s="86" t="s">
         <v>23</v>
       </c>
-      <c r="K31" s="89" t="s">
-        <v>24</v>
-      </c>
-      <c r="L31" s="150"/>
-    </row>
-    <row r="32" spans="1:12">
-      <c r="A32" s="96">
+      <c r="L31" s="146"/>
+    </row>
+    <row r="32" spans="1:12" ht="15" thickBot="1">
+      <c r="A32" s="93">
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
-      <c r="B32" s="153"/>
-      <c r="C32" s="144"/>
-      <c r="D32" s="86" t="s">
-        <v>115</v>
+      <c r="B32" s="149"/>
+      <c r="C32" s="140"/>
+      <c r="D32" s="83" t="s">
+        <v>114</v>
       </c>
       <c r="E32" s="51" t="s">
-        <v>114</v>
-      </c>
-      <c r="F32" s="133"/>
-      <c r="G32" s="59"/>
-      <c r="H32" s="97"/>
+        <v>113</v>
+      </c>
+      <c r="F32" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="G32" s="57"/>
+      <c r="H32" s="94"/>
       <c r="I32" s="51" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J32" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="K32" s="86" t="s">
         <v>23</v>
       </c>
-      <c r="K32" s="89" t="s">
-        <v>24</v>
-      </c>
-      <c r="L32" s="150"/>
-    </row>
-    <row r="33" spans="1:14">
-      <c r="A33" s="96">
+      <c r="L32" s="146"/>
+    </row>
+    <row r="33" spans="1:14" ht="15" thickBot="1">
+      <c r="A33" s="93">
         <f t="shared" si="1"/>
         <v>31</v>
       </c>
-      <c r="B33" s="153"/>
-      <c r="C33" s="144"/>
-      <c r="D33" s="86" t="s">
+      <c r="B33" s="149"/>
+      <c r="C33" s="140"/>
+      <c r="D33" s="83" t="s">
+        <v>115</v>
+      </c>
+      <c r="E33" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="F33" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="G33" s="57"/>
+      <c r="H33" s="94"/>
+      <c r="I33" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="J33" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="K33" s="86" t="s">
         <v>116</v>
       </c>
-      <c r="E33" s="51" t="s">
-        <v>116</v>
-      </c>
-      <c r="F33" s="133"/>
-      <c r="G33" s="59"/>
-      <c r="H33" s="97"/>
-      <c r="I33" s="51" t="s">
-        <v>116</v>
-      </c>
-      <c r="J33" s="51" t="s">
-        <v>23</v>
-      </c>
-      <c r="K33" s="89" t="s">
-        <v>117</v>
-      </c>
-      <c r="L33" s="150"/>
-    </row>
-    <row r="34" spans="1:14">
-      <c r="A34" s="96">
+      <c r="L33" s="146"/>
+    </row>
+    <row r="34" spans="1:14" ht="15" thickBot="1">
+      <c r="A34" s="93">
         <f t="shared" si="1"/>
         <v>32</v>
       </c>
-      <c r="B34" s="153"/>
-      <c r="C34" s="144"/>
-      <c r="D34" s="86" t="s">
-        <v>118</v>
+      <c r="B34" s="149"/>
+      <c r="C34" s="140"/>
+      <c r="D34" s="83" t="s">
+        <v>117</v>
       </c>
       <c r="E34" s="51" t="s">
-        <v>118</v>
-      </c>
-      <c r="F34" s="163"/>
-      <c r="G34" s="101" t="s">
-        <v>102</v>
-      </c>
-      <c r="H34" s="97"/>
+        <v>117</v>
+      </c>
+      <c r="F34" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="G34" s="98" t="s">
+        <v>101</v>
+      </c>
+      <c r="H34" s="94"/>
       <c r="I34" s="51" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J34" s="51" t="s">
-        <v>23</v>
-      </c>
-      <c r="K34" s="89" t="s">
-        <v>60</v>
-      </c>
-      <c r="L34" s="150"/>
-    </row>
-    <row r="35" spans="1:14">
-      <c r="A35" s="96">
+        <v>22</v>
+      </c>
+      <c r="K34" s="86" t="s">
+        <v>59</v>
+      </c>
+      <c r="L34" s="146"/>
+    </row>
+    <row r="35" spans="1:14" ht="15" thickBot="1">
+      <c r="A35" s="93">
         <f t="shared" si="1"/>
         <v>33</v>
       </c>
-      <c r="B35" s="153"/>
-      <c r="C35" s="144"/>
-      <c r="D35" s="87" t="s">
+      <c r="B35" s="149"/>
+      <c r="C35" s="140"/>
+      <c r="D35" s="84" t="s">
+        <v>118</v>
+      </c>
+      <c r="E35" s="51" t="s">
         <v>119</v>
       </c>
-      <c r="E35" s="51" t="s">
+      <c r="F35" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="G35" s="57"/>
+      <c r="H35" s="94"/>
+      <c r="I35" s="51" t="s">
         <v>120</v>
       </c>
-      <c r="F35" s="133"/>
-      <c r="G35" s="59"/>
-      <c r="H35" s="97"/>
-      <c r="I35" s="51" t="s">
+      <c r="J35" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="K35" s="86" t="s">
         <v>121</v>
       </c>
-      <c r="J35" s="51" t="s">
-        <v>23</v>
-      </c>
-      <c r="K35" s="89" t="s">
-        <v>122</v>
-      </c>
-      <c r="L35" s="150"/>
+      <c r="L35" s="146"/>
     </row>
     <row r="36" spans="1:14">
-      <c r="A36" s="96">
+      <c r="A36" s="93">
         <f t="shared" si="1"/>
         <v>34</v>
       </c>
-      <c r="B36" s="153"/>
-      <c r="C36" s="144"/>
-      <c r="D36" s="86" t="s">
+      <c r="B36" s="149"/>
+      <c r="C36" s="140"/>
+      <c r="D36" s="83" t="s">
+        <v>122</v>
+      </c>
+      <c r="E36" s="51" t="s">
         <v>123</v>
       </c>
-      <c r="E36" s="51" t="s">
+      <c r="F36" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="G36" s="57"/>
+      <c r="H36" s="94"/>
+      <c r="I36" s="51" t="s">
         <v>124</v>
       </c>
-      <c r="F36" s="133"/>
-      <c r="G36" s="59"/>
-      <c r="H36" s="97"/>
-      <c r="I36" s="51" t="s">
+      <c r="J36" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="K36" s="86" t="s">
         <v>125</v>
       </c>
-      <c r="J36" s="51" t="s">
-        <v>23</v>
-      </c>
-      <c r="K36" s="89" t="s">
-        <v>126</v>
-      </c>
-      <c r="L36" s="150"/>
+      <c r="L36" s="146"/>
     </row>
     <row r="37" spans="1:14">
-      <c r="A37" s="96">
+      <c r="A37" s="93">
         <f t="shared" si="1"/>
         <v>35</v>
       </c>
-      <c r="B37" s="153"/>
-      <c r="C37" s="144"/>
-      <c r="D37" s="88" t="s">
+      <c r="B37" s="149"/>
+      <c r="C37" s="140"/>
+      <c r="D37" s="85" t="s">
+        <v>126</v>
+      </c>
+      <c r="E37" s="50" t="s">
         <v>127</v>
       </c>
-      <c r="E37" s="50" t="s">
+      <c r="F37" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="G37" s="72" t="s">
+        <v>80</v>
+      </c>
+      <c r="H37" s="94"/>
+      <c r="I37" s="50" t="s">
+        <v>126</v>
+      </c>
+      <c r="J37" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="K37" s="104" t="s">
         <v>128</v>
       </c>
-      <c r="F37" s="50"/>
-      <c r="G37" s="74" t="s">
-        <v>81</v>
-      </c>
-      <c r="H37" s="97"/>
-      <c r="I37" s="50" t="s">
-        <v>127</v>
-      </c>
-      <c r="J37" s="51" t="s">
-        <v>23</v>
-      </c>
-      <c r="K37" s="107" t="s">
-        <v>129</v>
-      </c>
-      <c r="L37" s="150"/>
-    </row>
-    <row r="38" spans="1:14">
-      <c r="A38" s="96">
+      <c r="L37" s="146"/>
+    </row>
+    <row r="38" spans="1:14" ht="15" thickBot="1">
+      <c r="A38" s="93">
         <f t="shared" si="1"/>
         <v>36</v>
       </c>
-      <c r="B38" s="156"/>
-      <c r="C38" s="157"/>
-      <c r="D38" s="99" t="s">
+      <c r="B38" s="152"/>
+      <c r="C38" s="153"/>
+      <c r="D38" s="96" t="s">
+        <v>129</v>
+      </c>
+      <c r="E38" s="95" t="s">
         <v>130</v>
       </c>
-      <c r="E38" s="98" t="s">
+      <c r="F38" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="G38" s="98" t="s">
+        <v>101</v>
+      </c>
+      <c r="H38" s="99"/>
+      <c r="I38" s="95" t="s">
         <v>131</v>
       </c>
-      <c r="F38" s="164"/>
-      <c r="G38" s="101" t="s">
-        <v>102</v>
-      </c>
-      <c r="H38" s="102"/>
-      <c r="I38" s="98" t="s">
+      <c r="J38" s="97" t="s">
+        <v>22</v>
+      </c>
+      <c r="K38" s="95" t="s">
         <v>132</v>
       </c>
-      <c r="J38" s="100" t="s">
-        <v>23</v>
-      </c>
-      <c r="K38" s="98" t="s">
-        <v>133</v>
-      </c>
     </row>
     <row r="39" spans="1:14">
-      <c r="A39" s="58">
+      <c r="A39" s="56">
         <f t="shared" si="1"/>
         <v>37</v>
       </c>
-      <c r="B39" s="158" t="s">
+      <c r="B39" s="154" t="s">
+        <v>133</v>
+      </c>
+      <c r="C39" s="157" t="s">
         <v>134</v>
       </c>
-      <c r="C39" s="161" t="s">
+      <c r="D39" s="82" t="s">
         <v>135</v>
       </c>
-      <c r="D39" s="85" t="s">
+      <c r="E39" s="100" t="s">
         <v>136</v>
       </c>
-      <c r="E39" s="103" t="s">
+      <c r="F39" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G39" s="102"/>
+      <c r="H39" s="103"/>
+      <c r="I39" s="100" t="s">
         <v>137</v>
       </c>
-      <c r="F39" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="G39" s="105"/>
-      <c r="H39" s="106"/>
-      <c r="I39" s="103" t="s">
+      <c r="J39" s="101" t="s">
+        <v>22</v>
+      </c>
+      <c r="K39" s="100" t="s">
         <v>138</v>
-      </c>
-      <c r="J39" s="104" t="s">
-        <v>23</v>
-      </c>
-      <c r="K39" s="103" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="40" spans="1:14">
@@ -4530,31 +4539,31 @@
         <f t="shared" si="1"/>
         <v>38</v>
       </c>
-      <c r="B40" s="159"/>
-      <c r="C40" s="139"/>
-      <c r="D40" s="85" t="s">
+      <c r="B40" s="155"/>
+      <c r="C40" s="135"/>
+      <c r="D40" s="82" t="s">
+        <v>139</v>
+      </c>
+      <c r="E40" s="74" t="s">
         <v>140</v>
       </c>
-      <c r="E40" s="76" t="s">
+      <c r="F40" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G40" s="57"/>
+      <c r="H40" s="57"/>
+      <c r="I40" s="100" t="s">
         <v>141</v>
       </c>
-      <c r="F40" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="G40" s="59"/>
-      <c r="H40" s="59"/>
-      <c r="I40" s="103" t="s">
+      <c r="J40" s="101" t="s">
+        <v>22</v>
+      </c>
+      <c r="K40" s="100" t="s">
         <v>142</v>
       </c>
-      <c r="J40" s="104" t="s">
-        <v>23</v>
-      </c>
-      <c r="K40" s="103" t="s">
+      <c r="M40" s="107"/>
+      <c r="N40" s="105" t="s">
         <v>143</v>
-      </c>
-      <c r="M40" s="110"/>
-      <c r="N40" s="108" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="41" spans="1:14">
@@ -4562,31 +4571,31 @@
         <f t="shared" si="1"/>
         <v>39</v>
       </c>
-      <c r="B41" s="159"/>
-      <c r="C41" s="139"/>
+      <c r="B41" s="155"/>
+      <c r="C41" s="135"/>
       <c r="D41" s="36" t="s">
+        <v>144</v>
+      </c>
+      <c r="E41" s="65" t="s">
         <v>145</v>
       </c>
-      <c r="E41" s="67" t="s">
+      <c r="F41" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G41" s="57"/>
+      <c r="H41" s="57"/>
+      <c r="I41" s="105" t="s">
         <v>146</v>
       </c>
-      <c r="F41" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="G41" s="59"/>
-      <c r="H41" s="59"/>
-      <c r="I41" s="108" t="s">
+      <c r="J41" s="101" t="s">
+        <v>22</v>
+      </c>
+      <c r="K41" s="105" t="s">
+        <v>142</v>
+      </c>
+      <c r="M41" s="66"/>
+      <c r="N41" s="105" t="s">
         <v>147</v>
-      </c>
-      <c r="J41" s="104" t="s">
-        <v>23</v>
-      </c>
-      <c r="K41" s="108" t="s">
-        <v>143</v>
-      </c>
-      <c r="M41" s="68"/>
-      <c r="N41" s="108" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="42" spans="1:14">
@@ -4594,27 +4603,27 @@
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="B42" s="159"/>
-      <c r="C42" s="139"/>
+      <c r="B42" s="155"/>
+      <c r="C42" s="135"/>
       <c r="D42" s="36" t="s">
+        <v>148</v>
+      </c>
+      <c r="E42" s="65" t="s">
         <v>149</v>
       </c>
-      <c r="E42" s="67" t="s">
-        <v>150</v>
-      </c>
       <c r="F42" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="G42" s="59"/>
-      <c r="H42" s="59"/>
-      <c r="I42" s="108" t="s">
-        <v>149</v>
-      </c>
-      <c r="J42" s="104" t="s">
-        <v>23</v>
-      </c>
-      <c r="K42" s="108" t="s">
-        <v>143</v>
+        <v>32</v>
+      </c>
+      <c r="G42" s="57"/>
+      <c r="H42" s="57"/>
+      <c r="I42" s="105" t="s">
+        <v>148</v>
+      </c>
+      <c r="J42" s="101" t="s">
+        <v>22</v>
+      </c>
+      <c r="K42" s="105" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="43" spans="1:14">
@@ -4622,27 +4631,27 @@
         <f t="shared" si="1"/>
         <v>41</v>
       </c>
-      <c r="B43" s="159"/>
-      <c r="C43" s="139"/>
+      <c r="B43" s="155"/>
+      <c r="C43" s="135"/>
       <c r="D43" s="36" t="s">
+        <v>150</v>
+      </c>
+      <c r="E43" s="65" t="s">
         <v>151</v>
       </c>
-      <c r="E43" s="67" t="s">
+      <c r="F43" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G43" s="57"/>
+      <c r="H43" s="57"/>
+      <c r="I43" s="105" t="s">
         <v>152</v>
       </c>
-      <c r="F43" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="G43" s="59"/>
-      <c r="H43" s="59"/>
-      <c r="I43" s="108" t="s">
-        <v>153</v>
-      </c>
-      <c r="J43" s="104" t="s">
-        <v>23</v>
-      </c>
-      <c r="K43" s="108" t="s">
-        <v>143</v>
+      <c r="J43" s="101" t="s">
+        <v>22</v>
+      </c>
+      <c r="K43" s="105" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="44" spans="1:14">
@@ -4650,27 +4659,27 @@
         <f t="shared" si="1"/>
         <v>42</v>
       </c>
-      <c r="B44" s="159"/>
-      <c r="C44" s="139"/>
+      <c r="B44" s="155"/>
+      <c r="C44" s="135"/>
       <c r="D44" s="36" t="s">
+        <v>153</v>
+      </c>
+      <c r="E44" s="65" t="s">
         <v>154</v>
       </c>
-      <c r="E44" s="67" t="s">
+      <c r="F44" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G44" s="57"/>
+      <c r="H44" s="57"/>
+      <c r="I44" s="105" t="s">
         <v>155</v>
       </c>
-      <c r="F44" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="G44" s="59"/>
-      <c r="H44" s="59"/>
-      <c r="I44" s="108" t="s">
-        <v>156</v>
-      </c>
-      <c r="J44" s="104" t="s">
-        <v>23</v>
-      </c>
-      <c r="K44" s="108" t="s">
-        <v>143</v>
+      <c r="J44" s="101" t="s">
+        <v>22</v>
+      </c>
+      <c r="K44" s="105" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="45" spans="1:14">
@@ -4678,27 +4687,27 @@
         <f t="shared" si="1"/>
         <v>43</v>
       </c>
-      <c r="B45" s="159"/>
-      <c r="C45" s="139"/>
+      <c r="B45" s="155"/>
+      <c r="C45" s="135"/>
       <c r="D45" s="36" t="s">
+        <v>156</v>
+      </c>
+      <c r="E45" s="65" t="s">
         <v>157</v>
       </c>
-      <c r="E45" s="67" t="s">
-        <v>158</v>
-      </c>
       <c r="F45" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="G45" s="59"/>
-      <c r="H45" s="59"/>
-      <c r="I45" s="67" t="s">
-        <v>157</v>
-      </c>
-      <c r="J45" s="67" t="s">
-        <v>23</v>
-      </c>
-      <c r="K45" s="108" t="s">
-        <v>30</v>
+        <v>32</v>
+      </c>
+      <c r="G45" s="57"/>
+      <c r="H45" s="57"/>
+      <c r="I45" s="65" t="s">
+        <v>156</v>
+      </c>
+      <c r="J45" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="K45" s="105" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="46" spans="1:14">
@@ -4706,27 +4715,27 @@
         <f t="shared" si="1"/>
         <v>44</v>
       </c>
-      <c r="B46" s="159"/>
-      <c r="C46" s="139"/>
+      <c r="B46" s="155"/>
+      <c r="C46" s="135"/>
       <c r="D46" s="37" t="s">
+        <v>158</v>
+      </c>
+      <c r="E46" s="65" t="s">
         <v>159</v>
       </c>
-      <c r="E46" s="67" t="s">
+      <c r="F46" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G46" s="57"/>
+      <c r="H46" s="57"/>
+      <c r="I46" s="65" t="s">
         <v>160</v>
       </c>
-      <c r="F46" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="G46" s="59"/>
-      <c r="H46" s="59"/>
-      <c r="I46" s="67" t="s">
-        <v>161</v>
-      </c>
-      <c r="J46" s="67" t="s">
-        <v>23</v>
-      </c>
-      <c r="K46" s="108" t="s">
-        <v>126</v>
+      <c r="J46" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="K46" s="105" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="47" spans="1:14">
@@ -4734,27 +4743,27 @@
         <f t="shared" si="1"/>
         <v>45</v>
       </c>
-      <c r="B47" s="159"/>
-      <c r="C47" s="139"/>
+      <c r="B47" s="155"/>
+      <c r="C47" s="135"/>
       <c r="D47" s="37" t="s">
+        <v>161</v>
+      </c>
+      <c r="E47" s="65" t="s">
         <v>162</v>
       </c>
-      <c r="E47" s="67" t="s">
+      <c r="F47" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G47" s="57"/>
+      <c r="H47" s="57"/>
+      <c r="I47" s="65" t="s">
         <v>163</v>
       </c>
-      <c r="F47" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="G47" s="59"/>
-      <c r="H47" s="59"/>
-      <c r="I47" s="67" t="s">
-        <v>164</v>
-      </c>
-      <c r="J47" s="67" t="s">
-        <v>23</v>
-      </c>
-      <c r="K47" s="108" t="s">
-        <v>126</v>
+      <c r="J47" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="K47" s="105" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="48" spans="1:14">
@@ -4762,27 +4771,27 @@
         <f t="shared" si="1"/>
         <v>46</v>
       </c>
-      <c r="B48" s="159"/>
-      <c r="C48" s="139"/>
+      <c r="B48" s="155"/>
+      <c r="C48" s="135"/>
       <c r="D48" s="37" t="s">
+        <v>164</v>
+      </c>
+      <c r="E48" s="65" t="s">
         <v>165</v>
       </c>
-      <c r="E48" s="67" t="s">
-        <v>166</v>
-      </c>
       <c r="F48" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="G48" s="59"/>
-      <c r="H48" s="59"/>
-      <c r="I48" s="67" t="s">
+        <v>32</v>
+      </c>
+      <c r="G48" s="57"/>
+      <c r="H48" s="57"/>
+      <c r="I48" s="65" t="s">
+        <v>124</v>
+      </c>
+      <c r="J48" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="K48" s="105" t="s">
         <v>125</v>
-      </c>
-      <c r="J48" s="67" t="s">
-        <v>23</v>
-      </c>
-      <c r="K48" s="108" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="49" spans="1:11">
@@ -4790,27 +4799,29 @@
         <f t="shared" si="1"/>
         <v>47</v>
       </c>
-      <c r="B49" s="159"/>
-      <c r="C49" s="139" t="s">
+      <c r="B49" s="155"/>
+      <c r="C49" s="135" t="s">
+        <v>166</v>
+      </c>
+      <c r="D49" s="38" t="s">
         <v>167</v>
       </c>
-      <c r="D49" s="38" t="s">
+      <c r="E49" s="65" t="s">
         <v>168</v>
       </c>
-      <c r="E49" s="67" t="s">
-        <v>169</v>
-      </c>
-      <c r="F49" s="67"/>
-      <c r="G49" s="59"/>
-      <c r="H49" s="59"/>
-      <c r="I49" s="67" t="s">
-        <v>168</v>
-      </c>
-      <c r="J49" s="67" t="s">
-        <v>23</v>
-      </c>
-      <c r="K49" s="108" t="s">
-        <v>30</v>
+      <c r="F49" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G49" s="57"/>
+      <c r="H49" s="57"/>
+      <c r="I49" s="65" t="s">
+        <v>167</v>
+      </c>
+      <c r="J49" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="K49" s="105" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="50" spans="1:11">
@@ -4818,25 +4829,27 @@
         <f t="shared" si="1"/>
         <v>48</v>
       </c>
-      <c r="B50" s="159"/>
-      <c r="C50" s="139"/>
+      <c r="B50" s="155"/>
+      <c r="C50" s="135"/>
       <c r="D50" s="38" t="s">
+        <v>169</v>
+      </c>
+      <c r="E50" s="65" t="s">
         <v>170</v>
       </c>
-      <c r="E50" s="67" t="s">
-        <v>171</v>
-      </c>
-      <c r="F50" s="67"/>
-      <c r="G50" s="59"/>
-      <c r="H50" s="59"/>
-      <c r="I50" s="67" t="s">
-        <v>170</v>
-      </c>
-      <c r="J50" s="67" t="s">
-        <v>23</v>
-      </c>
-      <c r="K50" s="108" t="s">
-        <v>30</v>
+      <c r="F50" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G50" s="57"/>
+      <c r="H50" s="57"/>
+      <c r="I50" s="65" t="s">
+        <v>169</v>
+      </c>
+      <c r="J50" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="K50" s="105" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="51" spans="1:11">
@@ -4844,25 +4857,27 @@
         <f t="shared" si="1"/>
         <v>49</v>
       </c>
-      <c r="B51" s="159"/>
-      <c r="C51" s="139"/>
+      <c r="B51" s="155"/>
+      <c r="C51" s="135"/>
       <c r="D51" s="38" t="s">
+        <v>171</v>
+      </c>
+      <c r="E51" s="65" t="s">
         <v>172</v>
       </c>
-      <c r="E51" s="67" t="s">
+      <c r="F51" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G51" s="57"/>
+      <c r="H51" s="57"/>
+      <c r="I51" s="65" t="s">
         <v>173</v>
       </c>
-      <c r="F51" s="67"/>
-      <c r="G51" s="59"/>
-      <c r="H51" s="59"/>
-      <c r="I51" s="67" t="s">
-        <v>174</v>
-      </c>
-      <c r="J51" s="67" t="s">
-        <v>23</v>
-      </c>
-      <c r="K51" s="108" t="s">
-        <v>30</v>
+      <c r="J51" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="K51" s="105" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="52" spans="1:11">
@@ -4870,25 +4885,27 @@
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="B52" s="159"/>
-      <c r="C52" s="139"/>
+      <c r="B52" s="155"/>
+      <c r="C52" s="135"/>
       <c r="D52" s="39" t="s">
-        <v>175</v>
-      </c>
-      <c r="E52" s="67" t="s">
+        <v>174</v>
+      </c>
+      <c r="E52" s="65" t="s">
+        <v>162</v>
+      </c>
+      <c r="F52" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G52" s="57"/>
+      <c r="H52" s="57"/>
+      <c r="I52" s="65" t="s">
         <v>163</v>
       </c>
-      <c r="F52" s="67"/>
-      <c r="G52" s="59"/>
-      <c r="H52" s="59"/>
-      <c r="I52" s="67" t="s">
-        <v>164</v>
-      </c>
-      <c r="J52" s="67" t="s">
-        <v>23</v>
-      </c>
-      <c r="K52" s="108" t="s">
-        <v>126</v>
+      <c r="J52" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="K52" s="105" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="53" spans="1:11">
@@ -4896,25 +4913,27 @@
         <f t="shared" si="1"/>
         <v>51</v>
       </c>
-      <c r="B53" s="159"/>
-      <c r="C53" s="139"/>
+      <c r="B53" s="155"/>
+      <c r="C53" s="135"/>
       <c r="D53" s="39" t="s">
-        <v>176</v>
-      </c>
-      <c r="E53" s="67" t="s">
-        <v>160</v>
-      </c>
-      <c r="F53" s="67"/>
-      <c r="G53" s="59"/>
-      <c r="H53" s="59"/>
-      <c r="I53" s="67" t="s">
-        <v>176</v>
-      </c>
-      <c r="J53" s="67" t="s">
-        <v>23</v>
-      </c>
-      <c r="K53" s="108" t="s">
-        <v>126</v>
+        <v>175</v>
+      </c>
+      <c r="E53" s="65" t="s">
+        <v>159</v>
+      </c>
+      <c r="F53" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G53" s="57"/>
+      <c r="H53" s="57"/>
+      <c r="I53" s="65" t="s">
+        <v>175</v>
+      </c>
+      <c r="J53" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="K53" s="105" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -4922,25 +4941,27 @@
         <f t="shared" si="1"/>
         <v>52</v>
       </c>
-      <c r="B54" s="159"/>
-      <c r="C54" s="139"/>
+      <c r="B54" s="155"/>
+      <c r="C54" s="135"/>
       <c r="D54" s="39" t="s">
+        <v>176</v>
+      </c>
+      <c r="E54" s="65" t="s">
         <v>177</v>
       </c>
-      <c r="E54" s="67" t="s">
-        <v>178</v>
-      </c>
-      <c r="F54" s="67"/>
-      <c r="G54" s="59"/>
-      <c r="H54" s="59"/>
-      <c r="I54" s="67" t="s">
-        <v>177</v>
-      </c>
-      <c r="J54" s="67" t="s">
-        <v>23</v>
-      </c>
-      <c r="K54" s="108" t="s">
-        <v>126</v>
+      <c r="F54" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G54" s="57"/>
+      <c r="H54" s="57"/>
+      <c r="I54" s="65" t="s">
+        <v>176</v>
+      </c>
+      <c r="J54" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="K54" s="105" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="55" spans="1:11">
@@ -4948,47 +4969,51 @@
         <f t="shared" si="1"/>
         <v>53</v>
       </c>
-      <c r="B55" s="159"/>
-      <c r="C55" s="139"/>
+      <c r="B55" s="155"/>
+      <c r="C55" s="135"/>
       <c r="D55" s="40" t="s">
+        <v>178</v>
+      </c>
+      <c r="E55" s="66" t="s">
         <v>179</v>
       </c>
-      <c r="E55" s="68" t="s">
-        <v>180</v>
-      </c>
-      <c r="F55" s="68"/>
-      <c r="G55" s="116"/>
-      <c r="H55" s="116"/>
-      <c r="I55" s="68"/>
-      <c r="J55" s="68"/>
-      <c r="K55" s="109"/>
+      <c r="F55" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G55" s="113"/>
+      <c r="H55" s="113"/>
+      <c r="I55" s="66"/>
+      <c r="J55" s="66"/>
+      <c r="K55" s="106"/>
     </row>
     <row r="56" spans="1:11">
       <c r="A56" s="51">
         <f t="shared" si="1"/>
         <v>54</v>
       </c>
-      <c r="B56" s="159"/>
-      <c r="C56" s="139" t="s">
+      <c r="B56" s="155"/>
+      <c r="C56" s="135" t="s">
+        <v>180</v>
+      </c>
+      <c r="D56" s="36" t="s">
         <v>181</v>
       </c>
-      <c r="D56" s="36" t="s">
+      <c r="E56" s="65" t="s">
         <v>182</v>
       </c>
-      <c r="E56" s="67" t="s">
-        <v>183</v>
-      </c>
-      <c r="F56" s="67"/>
-      <c r="G56" s="59"/>
-      <c r="H56" s="59"/>
-      <c r="I56" s="67" t="s">
-        <v>182</v>
-      </c>
-      <c r="J56" s="67" t="s">
+      <c r="F56" s="159" t="s">
+        <v>32</v>
+      </c>
+      <c r="G56" s="57"/>
+      <c r="H56" s="57"/>
+      <c r="I56" s="65" t="s">
+        <v>181</v>
+      </c>
+      <c r="J56" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="K56" s="105" t="s">
         <v>23</v>
-      </c>
-      <c r="K56" s="108" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="57" spans="1:11">
@@ -4996,25 +5021,27 @@
         <f t="shared" si="1"/>
         <v>55</v>
       </c>
-      <c r="B57" s="159"/>
-      <c r="C57" s="139"/>
+      <c r="B57" s="155"/>
+      <c r="C57" s="135"/>
       <c r="D57" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="E57" s="65" t="s">
         <v>184</v>
       </c>
-      <c r="E57" s="67" t="s">
+      <c r="F57" s="159" t="s">
+        <v>32</v>
+      </c>
+      <c r="G57" s="57"/>
+      <c r="H57" s="57"/>
+      <c r="I57" s="65" t="s">
         <v>185</v>
       </c>
-      <c r="F57" s="67"/>
-      <c r="G57" s="59"/>
-      <c r="H57" s="59"/>
-      <c r="I57" s="67" t="s">
-        <v>186</v>
-      </c>
-      <c r="J57" s="67" t="s">
-        <v>23</v>
-      </c>
-      <c r="K57" s="108" t="s">
-        <v>30</v>
+      <c r="J57" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="K57" s="105" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="58" spans="1:11">
@@ -5022,25 +5049,27 @@
         <f t="shared" si="1"/>
         <v>56</v>
       </c>
-      <c r="B58" s="159"/>
-      <c r="C58" s="139"/>
+      <c r="B58" s="155"/>
+      <c r="C58" s="135"/>
       <c r="D58" s="37" t="s">
+        <v>186</v>
+      </c>
+      <c r="E58" s="65" t="s">
         <v>187</v>
       </c>
-      <c r="E58" s="67" t="s">
+      <c r="F58" s="159" t="s">
+        <v>32</v>
+      </c>
+      <c r="G58" s="57"/>
+      <c r="H58" s="57"/>
+      <c r="I58" s="65" t="s">
         <v>188</v>
       </c>
-      <c r="F58" s="67"/>
-      <c r="G58" s="59"/>
-      <c r="H58" s="59"/>
-      <c r="I58" s="67" t="s">
-        <v>189</v>
-      </c>
-      <c r="J58" s="67" t="s">
+      <c r="J58" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="K58" s="105" t="s">
         <v>23</v>
-      </c>
-      <c r="K58" s="108" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="59" spans="1:11">
@@ -5048,25 +5077,27 @@
         <f t="shared" si="1"/>
         <v>57</v>
       </c>
-      <c r="B59" s="159"/>
-      <c r="C59" s="139"/>
+      <c r="B59" s="155"/>
+      <c r="C59" s="135"/>
       <c r="D59" s="37" t="s">
+        <v>189</v>
+      </c>
+      <c r="E59" s="65" t="s">
         <v>190</v>
       </c>
-      <c r="E59" s="67" t="s">
-        <v>191</v>
-      </c>
-      <c r="F59" s="67"/>
-      <c r="G59" s="59"/>
-      <c r="H59" s="59"/>
-      <c r="I59" s="67" t="s">
-        <v>170</v>
-      </c>
-      <c r="J59" s="67" t="s">
-        <v>23</v>
-      </c>
-      <c r="K59" s="108" t="s">
-        <v>30</v>
+      <c r="F59" s="159" t="s">
+        <v>32</v>
+      </c>
+      <c r="G59" s="57"/>
+      <c r="H59" s="57"/>
+      <c r="I59" s="65" t="s">
+        <v>169</v>
+      </c>
+      <c r="J59" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="K59" s="105" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="60" spans="1:11">
@@ -5074,25 +5105,27 @@
         <f t="shared" si="1"/>
         <v>58</v>
       </c>
-      <c r="B60" s="159"/>
-      <c r="C60" s="139"/>
+      <c r="B60" s="155"/>
+      <c r="C60" s="135"/>
       <c r="D60" s="37" t="s">
-        <v>192</v>
-      </c>
-      <c r="E60" s="67" t="s">
-        <v>160</v>
-      </c>
-      <c r="F60" s="67"/>
-      <c r="G60" s="59"/>
-      <c r="H60" s="59"/>
-      <c r="I60" s="67" t="s">
-        <v>182</v>
-      </c>
-      <c r="J60" s="67" t="s">
+        <v>191</v>
+      </c>
+      <c r="E60" s="65" t="s">
+        <v>159</v>
+      </c>
+      <c r="F60" s="159" t="s">
+        <v>32</v>
+      </c>
+      <c r="G60" s="57"/>
+      <c r="H60" s="57"/>
+      <c r="I60" s="65" t="s">
+        <v>181</v>
+      </c>
+      <c r="J60" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="K60" s="105" t="s">
         <v>23</v>
-      </c>
-      <c r="K60" s="108" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="61" spans="1:11">
@@ -5100,27 +5133,29 @@
         <f t="shared" si="1"/>
         <v>59</v>
       </c>
-      <c r="B61" s="159"/>
-      <c r="C61" s="139" t="s">
+      <c r="B61" s="155"/>
+      <c r="C61" s="135" t="s">
+        <v>192</v>
+      </c>
+      <c r="D61" s="41" t="s">
         <v>193</v>
       </c>
-      <c r="D61" s="41" t="s">
+      <c r="E61" s="65" t="s">
         <v>194</v>
       </c>
-      <c r="E61" s="67" t="s">
+      <c r="F61" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G61" s="57"/>
+      <c r="H61" s="57"/>
+      <c r="I61" s="65" t="s">
+        <v>193</v>
+      </c>
+      <c r="J61" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="K61" s="105" t="s">
         <v>195</v>
-      </c>
-      <c r="F61" s="67"/>
-      <c r="G61" s="59"/>
-      <c r="H61" s="59"/>
-      <c r="I61" s="67" t="s">
-        <v>194</v>
-      </c>
-      <c r="J61" s="67" t="s">
-        <v>23</v>
-      </c>
-      <c r="K61" s="108" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="62" spans="1:11">
@@ -5128,25 +5163,27 @@
         <f t="shared" si="1"/>
         <v>60</v>
       </c>
-      <c r="B62" s="159"/>
-      <c r="C62" s="139"/>
+      <c r="B62" s="155"/>
+      <c r="C62" s="135"/>
       <c r="D62" s="42" t="s">
+        <v>196</v>
+      </c>
+      <c r="E62" s="65" t="s">
         <v>197</v>
       </c>
-      <c r="E62" s="67" t="s">
-        <v>198</v>
-      </c>
-      <c r="F62" s="67"/>
-      <c r="G62" s="59"/>
-      <c r="H62" s="59"/>
-      <c r="I62" s="67" t="s">
-        <v>197</v>
-      </c>
-      <c r="J62" s="67" t="s">
+      <c r="F62" s="159" t="s">
+        <v>32</v>
+      </c>
+      <c r="G62" s="57"/>
+      <c r="H62" s="57"/>
+      <c r="I62" s="65" t="s">
+        <v>196</v>
+      </c>
+      <c r="J62" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="K62" s="105" t="s">
         <v>23</v>
-      </c>
-      <c r="K62" s="108" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="63" spans="1:11">
@@ -5154,27 +5191,29 @@
         <f t="shared" si="1"/>
         <v>61</v>
       </c>
-      <c r="B63" s="159"/>
-      <c r="C63" s="139"/>
+      <c r="B63" s="155"/>
+      <c r="C63" s="135"/>
       <c r="D63" s="43" t="s">
+        <v>198</v>
+      </c>
+      <c r="E63" s="65" t="s">
         <v>199</v>
       </c>
-      <c r="E63" s="67" t="s">
+      <c r="F63" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G63" s="72" t="s">
         <v>200</v>
       </c>
-      <c r="F63" s="67"/>
-      <c r="G63" s="74" t="s">
+      <c r="H63" s="57"/>
+      <c r="I63" s="65" t="s">
         <v>201</v>
       </c>
-      <c r="H63" s="59"/>
-      <c r="I63" s="67" t="s">
-        <v>202</v>
-      </c>
-      <c r="J63" s="67" t="s">
-        <v>23</v>
-      </c>
-      <c r="K63" s="108" t="s">
-        <v>196</v>
+      <c r="J63" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="K63" s="105" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="64" spans="1:11">
@@ -5182,25 +5221,27 @@
         <f t="shared" si="1"/>
         <v>62</v>
       </c>
-      <c r="B64" s="159"/>
-      <c r="C64" s="139"/>
+      <c r="B64" s="155"/>
+      <c r="C64" s="135"/>
       <c r="D64" s="44" t="s">
+        <v>202</v>
+      </c>
+      <c r="E64" s="65" t="s">
         <v>203</v>
       </c>
-      <c r="E64" s="67" t="s">
-        <v>204</v>
-      </c>
-      <c r="F64" s="67"/>
+      <c r="F64" s="8" t="s">
+        <v>37</v>
+      </c>
       <c r="G64" s="51"/>
-      <c r="H64" s="59"/>
-      <c r="I64" s="67" t="s">
-        <v>203</v>
-      </c>
-      <c r="J64" s="67" t="s">
+      <c r="H64" s="57"/>
+      <c r="I64" s="65" t="s">
+        <v>202</v>
+      </c>
+      <c r="J64" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="K64" s="105" t="s">
         <v>23</v>
-      </c>
-      <c r="K64" s="108" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="65" spans="1:11">
@@ -5208,25 +5249,27 @@
         <f t="shared" si="1"/>
         <v>63</v>
       </c>
-      <c r="B65" s="159"/>
-      <c r="C65" s="139"/>
+      <c r="B65" s="155"/>
+      <c r="C65" s="135"/>
       <c r="D65" s="44" t="s">
+        <v>204</v>
+      </c>
+      <c r="E65" s="65" t="s">
         <v>205</v>
       </c>
-      <c r="E65" s="67" t="s">
-        <v>206</v>
-      </c>
-      <c r="F65" s="67"/>
-      <c r="G65" s="59"/>
-      <c r="H65" s="59"/>
-      <c r="I65" s="67" t="s">
-        <v>205</v>
-      </c>
-      <c r="J65" s="67" t="s">
+      <c r="F65" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G65" s="57"/>
+      <c r="H65" s="57"/>
+      <c r="I65" s="65" t="s">
+        <v>204</v>
+      </c>
+      <c r="J65" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="K65" s="105" t="s">
         <v>23</v>
-      </c>
-      <c r="K65" s="108" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="66" spans="1:11">
@@ -5234,25 +5277,27 @@
         <f t="shared" si="1"/>
         <v>64</v>
       </c>
-      <c r="B66" s="159"/>
-      <c r="C66" s="139"/>
+      <c r="B66" s="155"/>
+      <c r="C66" s="135"/>
       <c r="D66" s="44" t="s">
+        <v>206</v>
+      </c>
+      <c r="E66" s="65" t="s">
         <v>207</v>
       </c>
-      <c r="E66" s="67" t="s">
+      <c r="F66" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G66" s="57"/>
+      <c r="H66" s="57"/>
+      <c r="I66" s="65" t="s">
         <v>208</v>
       </c>
-      <c r="F66" s="67"/>
-      <c r="G66" s="59"/>
-      <c r="H66" s="59"/>
-      <c r="I66" s="67" t="s">
-        <v>209</v>
-      </c>
-      <c r="J66" s="67" t="s">
-        <v>23</v>
-      </c>
-      <c r="K66" s="108" t="s">
-        <v>60</v>
+      <c r="J66" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="K66" s="105" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="67" spans="1:11">
@@ -5260,25 +5305,27 @@
         <f t="shared" si="1"/>
         <v>65</v>
       </c>
-      <c r="B67" s="159"/>
-      <c r="C67" s="139"/>
+      <c r="B67" s="155"/>
+      <c r="C67" s="135"/>
       <c r="D67" s="44" t="s">
+        <v>209</v>
+      </c>
+      <c r="E67" s="65" t="s">
         <v>210</v>
       </c>
-      <c r="E67" s="67" t="s">
-        <v>211</v>
-      </c>
-      <c r="F67" s="67"/>
-      <c r="G67" s="59"/>
-      <c r="H67" s="59"/>
-      <c r="I67" s="67" t="s">
-        <v>210</v>
-      </c>
-      <c r="J67" s="67" t="s">
+      <c r="F67" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G67" s="57"/>
+      <c r="H67" s="57"/>
+      <c r="I67" s="65" t="s">
+        <v>209</v>
+      </c>
+      <c r="J67" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="K67" s="105" t="s">
         <v>23</v>
-      </c>
-      <c r="K67" s="108" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="68" spans="1:11">
@@ -5286,25 +5333,27 @@
         <f t="shared" si="1"/>
         <v>66</v>
       </c>
-      <c r="B68" s="159"/>
-      <c r="C68" s="139"/>
+      <c r="B68" s="155"/>
+      <c r="C68" s="135"/>
       <c r="D68" s="45" t="s">
+        <v>211</v>
+      </c>
+      <c r="E68" s="65" t="s">
         <v>212</v>
       </c>
-      <c r="E68" s="67" t="s">
-        <v>213</v>
-      </c>
-      <c r="F68" s="67"/>
-      <c r="G68" s="59"/>
-      <c r="H68" s="59"/>
-      <c r="I68" s="67" t="s">
-        <v>212</v>
-      </c>
-      <c r="J68" s="67" t="s">
+      <c r="F68" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="G68" s="57"/>
+      <c r="H68" s="57"/>
+      <c r="I68" s="65" t="s">
+        <v>211</v>
+      </c>
+      <c r="J68" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="K68" s="105" t="s">
         <v>23</v>
-      </c>
-      <c r="K68" s="108" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="69" spans="1:11">
@@ -5312,25 +5361,27 @@
         <f t="shared" si="1"/>
         <v>67</v>
       </c>
-      <c r="B69" s="159"/>
-      <c r="C69" s="139"/>
+      <c r="B69" s="155"/>
+      <c r="C69" s="135"/>
       <c r="D69" s="45" t="s">
+        <v>213</v>
+      </c>
+      <c r="E69" s="65" t="s">
         <v>214</v>
       </c>
-      <c r="E69" s="67" t="s">
-        <v>215</v>
-      </c>
-      <c r="F69" s="67"/>
-      <c r="G69" s="59"/>
-      <c r="H69" s="59"/>
-      <c r="I69" s="67" t="s">
-        <v>214</v>
-      </c>
-      <c r="J69" s="67" t="s">
+      <c r="F69" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="G69" s="57"/>
+      <c r="H69" s="57"/>
+      <c r="I69" s="65" t="s">
+        <v>213</v>
+      </c>
+      <c r="J69" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="K69" s="105" t="s">
         <v>23</v>
-      </c>
-      <c r="K69" s="108" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="70" spans="1:11">
@@ -5338,25 +5389,27 @@
         <f t="shared" si="1"/>
         <v>68</v>
       </c>
-      <c r="B70" s="159"/>
-      <c r="C70" s="139"/>
+      <c r="B70" s="155"/>
+      <c r="C70" s="135"/>
       <c r="D70" s="44" t="s">
+        <v>215</v>
+      </c>
+      <c r="E70" s="65" t="s">
         <v>216</v>
       </c>
-      <c r="E70" s="67" t="s">
+      <c r="F70" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G70" s="57"/>
+      <c r="H70" s="57"/>
+      <c r="I70" s="65" t="s">
         <v>217</v>
       </c>
-      <c r="F70" s="67"/>
-      <c r="G70" s="59"/>
-      <c r="H70" s="59"/>
-      <c r="I70" s="67" t="s">
-        <v>218</v>
-      </c>
-      <c r="J70" s="67" t="s">
-        <v>23</v>
-      </c>
-      <c r="K70" s="108" t="s">
-        <v>196</v>
+      <c r="J70" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="K70" s="105" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="71" spans="1:11">
@@ -5364,27 +5417,29 @@
         <f t="shared" si="1"/>
         <v>69</v>
       </c>
-      <c r="B71" s="159"/>
-      <c r="C71" s="139" t="s">
+      <c r="B71" s="155"/>
+      <c r="C71" s="135" t="s">
+        <v>218</v>
+      </c>
+      <c r="D71" s="45" t="s">
         <v>219</v>
       </c>
-      <c r="D71" s="45" t="s">
+      <c r="E71" s="65" t="s">
         <v>220</v>
       </c>
-      <c r="E71" s="67" t="s">
+      <c r="F71" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="G71" s="57"/>
+      <c r="H71" s="57"/>
+      <c r="I71" s="65" t="s">
+        <v>219</v>
+      </c>
+      <c r="J71" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="K71" s="105" t="s">
         <v>221</v>
-      </c>
-      <c r="F71" s="67"/>
-      <c r="G71" s="59"/>
-      <c r="H71" s="59"/>
-      <c r="I71" s="67" t="s">
-        <v>220</v>
-      </c>
-      <c r="J71" s="67" t="s">
-        <v>23</v>
-      </c>
-      <c r="K71" s="108" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="72" spans="1:11">
@@ -5392,25 +5447,27 @@
         <f t="shared" si="1"/>
         <v>70</v>
       </c>
-      <c r="B72" s="159"/>
-      <c r="C72" s="139"/>
+      <c r="B72" s="155"/>
+      <c r="C72" s="135"/>
       <c r="D72" s="46" t="s">
+        <v>222</v>
+      </c>
+      <c r="E72" s="65" t="s">
         <v>223</v>
       </c>
-      <c r="E72" s="67" t="s">
+      <c r="F72" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="G72" s="57"/>
+      <c r="H72" s="57"/>
+      <c r="I72" s="65" t="s">
         <v>224</v>
       </c>
-      <c r="F72" s="67"/>
-      <c r="G72" s="59"/>
-      <c r="H72" s="59"/>
-      <c r="I72" s="67" t="s">
-        <v>225</v>
-      </c>
-      <c r="J72" s="67" t="s">
-        <v>23</v>
-      </c>
-      <c r="K72" s="108" t="s">
-        <v>223</v>
+      <c r="J72" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="K72" s="105" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="73" spans="1:11">
@@ -5418,25 +5475,27 @@
         <f t="shared" si="1"/>
         <v>71</v>
       </c>
-      <c r="B73" s="159"/>
-      <c r="C73" s="139"/>
+      <c r="B73" s="155"/>
+      <c r="C73" s="135"/>
       <c r="D73" s="46" t="s">
+        <v>225</v>
+      </c>
+      <c r="E73" s="108" t="s">
         <v>226</v>
       </c>
-      <c r="E73" s="111" t="s">
-        <v>227</v>
-      </c>
-      <c r="F73" s="111"/>
-      <c r="G73" s="59"/>
-      <c r="H73" s="59"/>
-      <c r="I73" s="67" t="s">
-        <v>226</v>
-      </c>
-      <c r="J73" s="67" t="s">
-        <v>23</v>
-      </c>
-      <c r="K73" s="108" t="s">
-        <v>89</v>
+      <c r="F73" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="G73" s="57"/>
+      <c r="H73" s="57"/>
+      <c r="I73" s="65" t="s">
+        <v>225</v>
+      </c>
+      <c r="J73" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="K73" s="105" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="74" spans="1:11">
@@ -5444,25 +5503,27 @@
         <f t="shared" si="1"/>
         <v>72</v>
       </c>
-      <c r="B74" s="159"/>
-      <c r="C74" s="139"/>
+      <c r="B74" s="155"/>
+      <c r="C74" s="135"/>
       <c r="D74" s="46" t="s">
+        <v>227</v>
+      </c>
+      <c r="E74" s="108" t="s">
         <v>228</v>
       </c>
-      <c r="E74" s="111" t="s">
-        <v>229</v>
-      </c>
-      <c r="F74" s="111"/>
-      <c r="G74" s="59"/>
-      <c r="H74" s="59"/>
-      <c r="I74" s="67" t="s">
-        <v>226</v>
-      </c>
-      <c r="J74" s="67" t="s">
-        <v>23</v>
-      </c>
-      <c r="K74" s="108" t="s">
-        <v>89</v>
+      <c r="F74" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="G74" s="57"/>
+      <c r="H74" s="57"/>
+      <c r="I74" s="65" t="s">
+        <v>225</v>
+      </c>
+      <c r="J74" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="K74" s="105" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="75" spans="1:11">
@@ -5470,25 +5531,27 @@
         <f t="shared" si="1"/>
         <v>73</v>
       </c>
-      <c r="B75" s="159"/>
-      <c r="C75" s="139"/>
+      <c r="B75" s="155"/>
+      <c r="C75" s="135"/>
       <c r="D75" s="46" t="s">
+        <v>229</v>
+      </c>
+      <c r="E75" s="108" t="s">
         <v>230</v>
       </c>
-      <c r="E75" s="111" t="s">
-        <v>231</v>
-      </c>
-      <c r="F75" s="111"/>
-      <c r="G75" s="59"/>
-      <c r="H75" s="59"/>
-      <c r="I75" s="67" t="s">
-        <v>230</v>
-      </c>
-      <c r="J75" s="67" t="s">
-        <v>23</v>
-      </c>
-      <c r="K75" s="108" t="s">
-        <v>89</v>
+      <c r="F75" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="G75" s="57"/>
+      <c r="H75" s="57"/>
+      <c r="I75" s="65" t="s">
+        <v>229</v>
+      </c>
+      <c r="J75" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="K75" s="105" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="76" spans="1:11">
@@ -5496,25 +5559,27 @@
         <f t="shared" si="1"/>
         <v>74</v>
       </c>
-      <c r="B76" s="159"/>
-      <c r="C76" s="139"/>
+      <c r="B76" s="155"/>
+      <c r="C76" s="135"/>
       <c r="D76" s="45" t="s">
+        <v>231</v>
+      </c>
+      <c r="E76" s="65" t="s">
         <v>232</v>
       </c>
-      <c r="E76" s="67" t="s">
+      <c r="F76" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="G76" s="57"/>
+      <c r="H76" s="57"/>
+      <c r="I76" s="65" t="s">
         <v>233</v>
       </c>
-      <c r="F76" s="67"/>
-      <c r="G76" s="59"/>
-      <c r="H76" s="59"/>
-      <c r="I76" s="67" t="s">
-        <v>234</v>
-      </c>
-      <c r="J76" s="67" t="s">
-        <v>23</v>
-      </c>
-      <c r="K76" s="108" t="s">
-        <v>99</v>
+      <c r="J76" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="K76" s="105" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="77" spans="1:11">
@@ -5522,25 +5587,27 @@
         <f t="shared" si="1"/>
         <v>75</v>
       </c>
-      <c r="B77" s="159"/>
-      <c r="C77" s="139"/>
+      <c r="B77" s="155"/>
+      <c r="C77" s="135"/>
       <c r="D77" s="46" t="s">
+        <v>234</v>
+      </c>
+      <c r="E77" s="65" t="s">
         <v>235</v>
       </c>
-      <c r="E77" s="67" t="s">
-        <v>236</v>
-      </c>
-      <c r="F77" s="67"/>
-      <c r="G77" s="59"/>
-      <c r="H77" s="59"/>
-      <c r="I77" s="67" t="s">
-        <v>118</v>
-      </c>
-      <c r="J77" s="67" t="s">
-        <v>23</v>
-      </c>
-      <c r="K77" s="108" t="s">
-        <v>60</v>
+      <c r="F77" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="G77" s="57"/>
+      <c r="H77" s="57"/>
+      <c r="I77" s="65" t="s">
+        <v>117</v>
+      </c>
+      <c r="J77" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="K77" s="105" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="78" spans="1:11">
@@ -5548,25 +5615,27 @@
         <f t="shared" si="1"/>
         <v>76</v>
       </c>
-      <c r="B78" s="159"/>
-      <c r="C78" s="139"/>
+      <c r="B78" s="155"/>
+      <c r="C78" s="135"/>
       <c r="D78" s="46" t="s">
+        <v>236</v>
+      </c>
+      <c r="E78" s="65" t="s">
         <v>237</v>
       </c>
-      <c r="E78" s="67" t="s">
-        <v>238</v>
-      </c>
-      <c r="F78" s="67"/>
-      <c r="G78" s="59"/>
-      <c r="H78" s="59"/>
-      <c r="I78" s="67" t="s">
-        <v>118</v>
-      </c>
-      <c r="J78" s="67" t="s">
-        <v>23</v>
-      </c>
-      <c r="K78" s="108" t="s">
-        <v>60</v>
+      <c r="F78" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="G78" s="57"/>
+      <c r="H78" s="57"/>
+      <c r="I78" s="65" t="s">
+        <v>117</v>
+      </c>
+      <c r="J78" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="K78" s="105" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="79" spans="1:11">
@@ -5574,25 +5643,27 @@
         <f t="shared" si="1"/>
         <v>77</v>
       </c>
-      <c r="B79" s="159"/>
-      <c r="C79" s="139"/>
+      <c r="B79" s="155"/>
+      <c r="C79" s="135"/>
       <c r="D79" s="46" t="s">
-        <v>239</v>
-      </c>
-      <c r="E79" s="67" t="s">
-        <v>63</v>
-      </c>
-      <c r="F79" s="67"/>
-      <c r="G79" s="59"/>
-      <c r="H79" s="59"/>
-      <c r="I79" s="67" t="s">
-        <v>63</v>
-      </c>
-      <c r="J79" s="67" t="s">
-        <v>23</v>
-      </c>
-      <c r="K79" s="108" t="s">
-        <v>60</v>
+        <v>238</v>
+      </c>
+      <c r="E79" s="65" t="s">
+        <v>62</v>
+      </c>
+      <c r="F79" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="G79" s="57"/>
+      <c r="H79" s="57"/>
+      <c r="I79" s="65" t="s">
+        <v>62</v>
+      </c>
+      <c r="J79" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="K79" s="105" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="80" spans="1:11">
@@ -5600,27 +5671,29 @@
         <f t="shared" ref="A80:A135" si="2">A79+1</f>
         <v>78</v>
       </c>
-      <c r="B80" s="159"/>
-      <c r="C80" s="139" t="s">
+      <c r="B80" s="155"/>
+      <c r="C80" s="135" t="s">
+        <v>239</v>
+      </c>
+      <c r="D80" s="36" t="s">
         <v>240</v>
       </c>
-      <c r="D80" s="36" t="s">
+      <c r="E80" s="67" t="s">
         <v>241</v>
       </c>
-      <c r="E80" s="69" t="s">
+      <c r="F80" s="159" t="s">
+        <v>32</v>
+      </c>
+      <c r="G80" s="57"/>
+      <c r="H80" s="57"/>
+      <c r="I80" s="67" t="s">
         <v>242</v>
       </c>
-      <c r="F80" s="69"/>
-      <c r="G80" s="59"/>
-      <c r="H80" s="59"/>
-      <c r="I80" s="69" t="s">
-        <v>243</v>
-      </c>
-      <c r="J80" s="69" t="s">
-        <v>23</v>
-      </c>
-      <c r="K80" s="81" t="s">
-        <v>30</v>
+      <c r="J80" s="67" t="s">
+        <v>22</v>
+      </c>
+      <c r="K80" s="78" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5628,25 +5701,27 @@
         <f t="shared" si="2"/>
         <v>79</v>
       </c>
-      <c r="B81" s="159"/>
-      <c r="C81" s="139"/>
+      <c r="B81" s="155"/>
+      <c r="C81" s="135"/>
       <c r="D81" s="36" t="s">
+        <v>243</v>
+      </c>
+      <c r="E81" s="67" t="s">
         <v>244</v>
       </c>
-      <c r="E81" s="69" t="s">
+      <c r="F81" s="159" t="s">
+        <v>32</v>
+      </c>
+      <c r="G81" s="57"/>
+      <c r="H81" s="57"/>
+      <c r="I81" s="67" t="s">
         <v>245</v>
       </c>
-      <c r="F81" s="69"/>
-      <c r="G81" s="59"/>
-      <c r="H81" s="59"/>
-      <c r="I81" s="69" t="s">
+      <c r="J81" s="67" t="s">
+        <v>22</v>
+      </c>
+      <c r="K81" s="78" t="s">
         <v>246</v>
-      </c>
-      <c r="J81" s="69" t="s">
-        <v>23</v>
-      </c>
-      <c r="K81" s="81" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5654,25 +5729,27 @@
         <f t="shared" si="2"/>
         <v>80</v>
       </c>
-      <c r="B82" s="159"/>
-      <c r="C82" s="139"/>
+      <c r="B82" s="155"/>
+      <c r="C82" s="135"/>
       <c r="D82" s="36" t="s">
+        <v>247</v>
+      </c>
+      <c r="E82" s="67" t="s">
         <v>248</v>
       </c>
-      <c r="E82" s="69" t="s">
-        <v>249</v>
-      </c>
-      <c r="F82" s="69"/>
-      <c r="G82" s="59"/>
-      <c r="H82" s="59"/>
-      <c r="I82" s="69" t="s">
-        <v>243</v>
-      </c>
-      <c r="J82" s="69" t="s">
-        <v>23</v>
-      </c>
-      <c r="K82" s="81" t="s">
-        <v>30</v>
+      <c r="F82" s="159" t="s">
+        <v>32</v>
+      </c>
+      <c r="G82" s="57"/>
+      <c r="H82" s="57"/>
+      <c r="I82" s="67" t="s">
+        <v>242</v>
+      </c>
+      <c r="J82" s="67" t="s">
+        <v>22</v>
+      </c>
+      <c r="K82" s="78" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5680,25 +5757,27 @@
         <f t="shared" si="2"/>
         <v>81</v>
       </c>
-      <c r="B83" s="159"/>
-      <c r="C83" s="139"/>
+      <c r="B83" s="155"/>
+      <c r="C83" s="135"/>
       <c r="D83" s="36" t="s">
+        <v>249</v>
+      </c>
+      <c r="E83" s="67" t="s">
         <v>250</v>
       </c>
-      <c r="E83" s="69" t="s">
+      <c r="F83" s="159" t="s">
+        <v>32</v>
+      </c>
+      <c r="G83" s="57"/>
+      <c r="H83" s="57"/>
+      <c r="I83" s="67" t="s">
         <v>251</v>
       </c>
-      <c r="F83" s="69"/>
-      <c r="G83" s="59"/>
-      <c r="H83" s="59"/>
-      <c r="I83" s="69" t="s">
-        <v>252</v>
-      </c>
-      <c r="J83" s="69" t="s">
-        <v>23</v>
-      </c>
-      <c r="K83" s="81" t="s">
-        <v>139</v>
+      <c r="J83" s="67" t="s">
+        <v>22</v>
+      </c>
+      <c r="K83" s="78" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5706,25 +5785,27 @@
         <f t="shared" si="2"/>
         <v>82</v>
       </c>
-      <c r="B84" s="159"/>
-      <c r="C84" s="139"/>
+      <c r="B84" s="155"/>
+      <c r="C84" s="135"/>
       <c r="D84" s="36" t="s">
+        <v>252</v>
+      </c>
+      <c r="E84" s="67" t="s">
         <v>253</v>
       </c>
-      <c r="E84" s="69" t="s">
+      <c r="F84" s="159" t="s">
+        <v>32</v>
+      </c>
+      <c r="G84" s="57"/>
+      <c r="H84" s="57"/>
+      <c r="I84" s="67" t="s">
         <v>254</v>
       </c>
-      <c r="F84" s="69"/>
-      <c r="G84" s="59"/>
-      <c r="H84" s="59"/>
-      <c r="I84" s="69" t="s">
-        <v>255</v>
-      </c>
-      <c r="J84" s="69" t="s">
-        <v>23</v>
-      </c>
-      <c r="K84" s="81" t="s">
-        <v>139</v>
+      <c r="J84" s="67" t="s">
+        <v>22</v>
+      </c>
+      <c r="K84" s="78" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5732,25 +5813,27 @@
         <f t="shared" si="2"/>
         <v>83</v>
       </c>
-      <c r="B85" s="159"/>
-      <c r="C85" s="139"/>
+      <c r="B85" s="155"/>
+      <c r="C85" s="135"/>
       <c r="D85" s="36" t="s">
+        <v>255</v>
+      </c>
+      <c r="E85" s="67" t="s">
         <v>256</v>
       </c>
-      <c r="E85" s="69" t="s">
+      <c r="F85" s="159" t="s">
+        <v>32</v>
+      </c>
+      <c r="G85" s="57"/>
+      <c r="H85" s="57"/>
+      <c r="I85" s="67" t="s">
         <v>257</v>
       </c>
-      <c r="F85" s="69"/>
-      <c r="G85" s="59"/>
-      <c r="H85" s="59"/>
-      <c r="I85" s="69" t="s">
-        <v>258</v>
-      </c>
-      <c r="J85" s="69" t="s">
-        <v>23</v>
-      </c>
-      <c r="K85" s="81" t="s">
-        <v>139</v>
+      <c r="J85" s="67" t="s">
+        <v>22</v>
+      </c>
+      <c r="K85" s="78" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5758,25 +5841,27 @@
         <f t="shared" si="2"/>
         <v>84</v>
       </c>
-      <c r="B86" s="159"/>
-      <c r="C86" s="139"/>
+      <c r="B86" s="155"/>
+      <c r="C86" s="135"/>
       <c r="D86" s="36" t="s">
+        <v>258</v>
+      </c>
+      <c r="E86" s="67" t="s">
         <v>259</v>
       </c>
-      <c r="E86" s="69" t="s">
-        <v>260</v>
-      </c>
-      <c r="F86" s="69"/>
-      <c r="G86" s="59"/>
-      <c r="H86" s="59"/>
-      <c r="I86" s="69" t="s">
-        <v>259</v>
-      </c>
-      <c r="J86" s="69" t="s">
-        <v>23</v>
-      </c>
-      <c r="K86" s="81" t="s">
-        <v>30</v>
+      <c r="F86" s="159" t="s">
+        <v>32</v>
+      </c>
+      <c r="G86" s="57"/>
+      <c r="H86" s="57"/>
+      <c r="I86" s="67" t="s">
+        <v>258</v>
+      </c>
+      <c r="J86" s="67" t="s">
+        <v>22</v>
+      </c>
+      <c r="K86" s="78" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5784,25 +5869,27 @@
         <f t="shared" si="2"/>
         <v>85</v>
       </c>
-      <c r="B87" s="159"/>
-      <c r="C87" s="139"/>
+      <c r="B87" s="155"/>
+      <c r="C87" s="135"/>
       <c r="D87" s="36" t="s">
+        <v>260</v>
+      </c>
+      <c r="E87" s="67" t="s">
         <v>261</v>
       </c>
-      <c r="E87" s="69" t="s">
+      <c r="F87" s="159" t="s">
+        <v>32</v>
+      </c>
+      <c r="G87" s="57"/>
+      <c r="H87" s="57"/>
+      <c r="I87" s="67" t="s">
         <v>262</v>
       </c>
-      <c r="F87" s="69"/>
-      <c r="G87" s="59"/>
-      <c r="H87" s="59"/>
-      <c r="I87" s="69" t="s">
-        <v>263</v>
-      </c>
-      <c r="J87" s="69" t="s">
-        <v>23</v>
-      </c>
-      <c r="K87" s="81" t="s">
-        <v>247</v>
+      <c r="J87" s="67" t="s">
+        <v>22</v>
+      </c>
+      <c r="K87" s="78" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5810,25 +5897,27 @@
         <f t="shared" si="2"/>
         <v>86</v>
       </c>
-      <c r="B88" s="159"/>
-      <c r="C88" s="139"/>
+      <c r="B88" s="155"/>
+      <c r="C88" s="135"/>
       <c r="D88" s="36" t="s">
+        <v>263</v>
+      </c>
+      <c r="E88" s="67" t="s">
         <v>264</v>
       </c>
-      <c r="E88" s="69" t="s">
+      <c r="F88" s="159" t="s">
+        <v>32</v>
+      </c>
+      <c r="G88" s="57"/>
+      <c r="H88" s="57"/>
+      <c r="I88" s="67" t="s">
         <v>265</v>
       </c>
-      <c r="F88" s="69"/>
-      <c r="G88" s="59"/>
-      <c r="H88" s="59"/>
-      <c r="I88" s="69" t="s">
-        <v>266</v>
-      </c>
-      <c r="J88" s="69" t="s">
-        <v>23</v>
-      </c>
-      <c r="K88" s="81" t="s">
-        <v>247</v>
+      <c r="J88" s="67" t="s">
+        <v>22</v>
+      </c>
+      <c r="K88" s="78" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5836,25 +5925,27 @@
         <f t="shared" si="2"/>
         <v>87</v>
       </c>
-      <c r="B89" s="159"/>
-      <c r="C89" s="139"/>
+      <c r="B89" s="155"/>
+      <c r="C89" s="135"/>
       <c r="D89" s="36" t="s">
-        <v>164</v>
-      </c>
-      <c r="E89" s="69" t="s">
         <v>163</v>
       </c>
-      <c r="F89" s="69"/>
-      <c r="G89" s="59"/>
-      <c r="H89" s="59"/>
-      <c r="I89" s="69" t="s">
-        <v>164</v>
-      </c>
-      <c r="J89" s="69" t="s">
-        <v>23</v>
-      </c>
-      <c r="K89" s="81" t="s">
-        <v>126</v>
+      <c r="E89" s="67" t="s">
+        <v>162</v>
+      </c>
+      <c r="F89" s="159" t="s">
+        <v>32</v>
+      </c>
+      <c r="G89" s="57"/>
+      <c r="H89" s="57"/>
+      <c r="I89" s="67" t="s">
+        <v>163</v>
+      </c>
+      <c r="J89" s="67" t="s">
+        <v>22</v>
+      </c>
+      <c r="K89" s="78" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5862,25 +5953,27 @@
         <f t="shared" si="2"/>
         <v>88</v>
       </c>
-      <c r="B90" s="159"/>
-      <c r="C90" s="139"/>
+      <c r="B90" s="155"/>
+      <c r="C90" s="135"/>
       <c r="D90" s="37" t="s">
+        <v>266</v>
+      </c>
+      <c r="E90" s="67" t="s">
         <v>267</v>
       </c>
-      <c r="E90" s="69" t="s">
-        <v>268</v>
-      </c>
-      <c r="F90" s="69"/>
-      <c r="G90" s="59"/>
-      <c r="H90" s="59"/>
-      <c r="I90" s="69" t="s">
-        <v>267</v>
-      </c>
-      <c r="J90" s="69" t="s">
-        <v>23</v>
-      </c>
-      <c r="K90" s="120" t="s">
-        <v>30</v>
+      <c r="F90" s="159" t="s">
+        <v>32</v>
+      </c>
+      <c r="G90" s="57"/>
+      <c r="H90" s="57"/>
+      <c r="I90" s="67" t="s">
+        <v>266</v>
+      </c>
+      <c r="J90" s="67" t="s">
+        <v>22</v>
+      </c>
+      <c r="K90" s="117" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -5888,27 +5981,29 @@
         <f t="shared" si="2"/>
         <v>89</v>
       </c>
-      <c r="B91" s="159"/>
+      <c r="B91" s="155"/>
       <c r="C91" s="35" t="s">
+        <v>268</v>
+      </c>
+      <c r="D91" s="36" t="s">
         <v>269</v>
       </c>
-      <c r="D91" s="36" t="s">
+      <c r="E91" s="67" t="s">
         <v>270</v>
       </c>
-      <c r="E91" s="69" t="s">
-        <v>271</v>
-      </c>
-      <c r="F91" s="69"/>
-      <c r="G91" s="59"/>
-      <c r="H91" s="59"/>
-      <c r="I91" s="69" t="s">
-        <v>270</v>
-      </c>
-      <c r="J91" s="69" t="s">
-        <v>23</v>
-      </c>
-      <c r="K91" s="81" t="s">
-        <v>30</v>
+      <c r="F91" s="159" t="s">
+        <v>32</v>
+      </c>
+      <c r="G91" s="57"/>
+      <c r="H91" s="57"/>
+      <c r="I91" s="67" t="s">
+        <v>269</v>
+      </c>
+      <c r="J91" s="67" t="s">
+        <v>22</v>
+      </c>
+      <c r="K91" s="78" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -5916,27 +6011,29 @@
         <f t="shared" si="2"/>
         <v>90</v>
       </c>
-      <c r="B92" s="159"/>
+      <c r="B92" s="155"/>
       <c r="C92" s="35" t="s">
+        <v>271</v>
+      </c>
+      <c r="D92" s="36" t="s">
         <v>272</v>
       </c>
-      <c r="D92" s="36" t="s">
+      <c r="E92" s="67" t="s">
         <v>273</v>
       </c>
-      <c r="E92" s="69" t="s">
+      <c r="F92" s="159" t="s">
+        <v>32</v>
+      </c>
+      <c r="G92" s="57"/>
+      <c r="H92" s="57"/>
+      <c r="I92" s="67" t="s">
+        <v>272</v>
+      </c>
+      <c r="J92" s="67" t="s">
+        <v>22</v>
+      </c>
+      <c r="K92" s="78" t="s">
         <v>274</v>
-      </c>
-      <c r="F92" s="69"/>
-      <c r="G92" s="59"/>
-      <c r="H92" s="59"/>
-      <c r="I92" s="69" t="s">
-        <v>273</v>
-      </c>
-      <c r="J92" s="69" t="s">
-        <v>23</v>
-      </c>
-      <c r="K92" s="81" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -5944,27 +6041,29 @@
         <f t="shared" si="2"/>
         <v>91</v>
       </c>
-      <c r="B93" s="159"/>
-      <c r="C93" s="139" t="s">
+      <c r="B93" s="155"/>
+      <c r="C93" s="135" t="s">
+        <v>275</v>
+      </c>
+      <c r="D93" s="36" t="s">
         <v>276</v>
       </c>
-      <c r="D93" s="36" t="s">
+      <c r="E93" s="67" t="s">
         <v>277</v>
       </c>
-      <c r="E93" s="69" t="s">
-        <v>278</v>
-      </c>
-      <c r="F93" s="69"/>
-      <c r="G93" s="59"/>
-      <c r="H93" s="59"/>
-      <c r="I93" s="69" t="s">
-        <v>277</v>
-      </c>
-      <c r="J93" s="69" t="s">
-        <v>23</v>
-      </c>
-      <c r="K93" s="81" t="s">
-        <v>126</v>
+      <c r="F93" s="159" t="s">
+        <v>32</v>
+      </c>
+      <c r="G93" s="57"/>
+      <c r="H93" s="57"/>
+      <c r="I93" s="67" t="s">
+        <v>276</v>
+      </c>
+      <c r="J93" s="67" t="s">
+        <v>22</v>
+      </c>
+      <c r="K93" s="78" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -5972,25 +6071,27 @@
         <f t="shared" si="2"/>
         <v>92</v>
       </c>
-      <c r="B94" s="159"/>
-      <c r="C94" s="139"/>
+      <c r="B94" s="155"/>
+      <c r="C94" s="135"/>
       <c r="D94" s="36" t="s">
+        <v>278</v>
+      </c>
+      <c r="E94" s="67" t="s">
         <v>279</v>
       </c>
-      <c r="E94" s="69" t="s">
+      <c r="F94" s="159" t="s">
+        <v>32</v>
+      </c>
+      <c r="G94" s="57"/>
+      <c r="H94" s="57"/>
+      <c r="I94" s="67" t="s">
         <v>280</v>
       </c>
-      <c r="F94" s="69"/>
-      <c r="G94" s="59"/>
-      <c r="H94" s="59"/>
-      <c r="I94" s="69" t="s">
-        <v>281</v>
-      </c>
-      <c r="J94" s="69" t="s">
-        <v>23</v>
-      </c>
-      <c r="K94" s="81" t="s">
-        <v>30</v>
+      <c r="J94" s="67" t="s">
+        <v>22</v>
+      </c>
+      <c r="K94" s="78" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="95" spans="1:16" ht="16.5">
@@ -5998,54 +6099,58 @@
         <f t="shared" si="2"/>
         <v>93</v>
       </c>
-      <c r="B95" s="159"/>
-      <c r="C95" s="139"/>
+      <c r="B95" s="155"/>
+      <c r="C95" s="135"/>
       <c r="D95" s="36" t="s">
+        <v>281</v>
+      </c>
+      <c r="E95" s="67" t="s">
         <v>282</v>
       </c>
-      <c r="E95" s="69" t="s">
-        <v>283</v>
-      </c>
-      <c r="F95" s="69"/>
-      <c r="G95" s="59"/>
-      <c r="H95" s="59"/>
-      <c r="I95" s="69" t="s">
-        <v>282</v>
-      </c>
-      <c r="J95" s="69" t="s">
-        <v>23</v>
-      </c>
-      <c r="K95" s="81" t="s">
-        <v>30</v>
-      </c>
-      <c r="N95" s="148"/>
-      <c r="O95" s="149"/>
-      <c r="P95" s="149"/>
+      <c r="F95" s="159" t="s">
+        <v>32</v>
+      </c>
+      <c r="G95" s="57"/>
+      <c r="H95" s="57"/>
+      <c r="I95" s="67" t="s">
+        <v>281</v>
+      </c>
+      <c r="J95" s="67" t="s">
+        <v>22</v>
+      </c>
+      <c r="K95" s="78" t="s">
+        <v>29</v>
+      </c>
+      <c r="N95" s="144"/>
+      <c r="O95" s="145"/>
+      <c r="P95" s="145"/>
     </row>
     <row r="96" spans="1:16" ht="15">
       <c r="A96" s="51">
         <f t="shared" si="2"/>
         <v>94</v>
       </c>
-      <c r="B96" s="159"/>
-      <c r="C96" s="139"/>
+      <c r="B96" s="155"/>
+      <c r="C96" s="135"/>
       <c r="D96" s="36" t="s">
+        <v>124</v>
+      </c>
+      <c r="E96" s="67" t="s">
+        <v>283</v>
+      </c>
+      <c r="F96" s="159" t="s">
+        <v>32</v>
+      </c>
+      <c r="G96" s="57"/>
+      <c r="H96" s="57"/>
+      <c r="I96" s="67" t="s">
+        <v>276</v>
+      </c>
+      <c r="J96" s="67" t="s">
+        <v>22</v>
+      </c>
+      <c r="K96" s="78" t="s">
         <v>125</v>
-      </c>
-      <c r="E96" s="69" t="s">
-        <v>284</v>
-      </c>
-      <c r="F96" s="69"/>
-      <c r="G96" s="59"/>
-      <c r="H96" s="59"/>
-      <c r="I96" s="69" t="s">
-        <v>277</v>
-      </c>
-      <c r="J96" s="69" t="s">
-        <v>23</v>
-      </c>
-      <c r="K96" s="81" t="s">
-        <v>126</v>
       </c>
       <c r="N96" s="22"/>
     </row>
@@ -6054,27 +6159,29 @@
         <f t="shared" si="2"/>
         <v>95</v>
       </c>
-      <c r="B97" s="159"/>
-      <c r="C97" s="139" t="s">
+      <c r="B97" s="155"/>
+      <c r="C97" s="135" t="s">
+        <v>284</v>
+      </c>
+      <c r="D97" s="44" t="s">
         <v>285</v>
       </c>
-      <c r="D97" s="44" t="s">
+      <c r="E97" s="67" t="s">
         <v>286</v>
       </c>
-      <c r="E97" s="69" t="s">
-        <v>287</v>
-      </c>
-      <c r="F97" s="69"/>
-      <c r="G97" s="59"/>
-      <c r="H97" s="59"/>
-      <c r="I97" s="69" t="s">
-        <v>286</v>
-      </c>
-      <c r="J97" s="69" t="s">
+      <c r="F97" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G97" s="57"/>
+      <c r="H97" s="57"/>
+      <c r="I97" s="67" t="s">
+        <v>285</v>
+      </c>
+      <c r="J97" s="67" t="s">
+        <v>22</v>
+      </c>
+      <c r="K97" s="78" t="s">
         <v>23</v>
-      </c>
-      <c r="K97" s="81" t="s">
-        <v>24</v>
       </c>
       <c r="N97" s="22"/>
     </row>
@@ -6083,25 +6190,27 @@
         <f t="shared" si="2"/>
         <v>96</v>
       </c>
-      <c r="B98" s="159"/>
-      <c r="C98" s="139"/>
+      <c r="B98" s="155"/>
+      <c r="C98" s="135"/>
       <c r="D98" s="44" t="s">
+        <v>287</v>
+      </c>
+      <c r="E98" s="67" t="s">
         <v>288</v>
       </c>
-      <c r="E98" s="69" t="s">
-        <v>289</v>
-      </c>
-      <c r="F98" s="69"/>
-      <c r="G98" s="59"/>
-      <c r="H98" s="59"/>
-      <c r="I98" s="69" t="s">
-        <v>288</v>
-      </c>
-      <c r="J98" s="69" t="s">
+      <c r="F98" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G98" s="57"/>
+      <c r="H98" s="57"/>
+      <c r="I98" s="67" t="s">
+        <v>287</v>
+      </c>
+      <c r="J98" s="67" t="s">
+        <v>22</v>
+      </c>
+      <c r="K98" s="78" t="s">
         <v>23</v>
-      </c>
-      <c r="K98" s="81" t="s">
-        <v>24</v>
       </c>
       <c r="N98" s="22"/>
     </row>
@@ -6110,25 +6219,27 @@
         <f t="shared" si="2"/>
         <v>97</v>
       </c>
-      <c r="B99" s="159"/>
-      <c r="C99" s="139"/>
+      <c r="B99" s="155"/>
+      <c r="C99" s="135"/>
       <c r="D99" s="44" t="s">
+        <v>289</v>
+      </c>
+      <c r="E99" s="67" t="s">
         <v>290</v>
       </c>
-      <c r="E99" s="69" t="s">
-        <v>291</v>
-      </c>
-      <c r="F99" s="69"/>
-      <c r="G99" s="59"/>
-      <c r="H99" s="59"/>
-      <c r="I99" s="69" t="s">
-        <v>290</v>
-      </c>
-      <c r="J99" s="69" t="s">
-        <v>23</v>
-      </c>
-      <c r="K99" s="81" t="s">
-        <v>196</v>
+      <c r="F99" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G99" s="57"/>
+      <c r="H99" s="57"/>
+      <c r="I99" s="67" t="s">
+        <v>289</v>
+      </c>
+      <c r="J99" s="67" t="s">
+        <v>22</v>
+      </c>
+      <c r="K99" s="78" t="s">
+        <v>195</v>
       </c>
       <c r="N99" s="23"/>
     </row>
@@ -6137,27 +6248,29 @@
         <f t="shared" si="2"/>
         <v>98</v>
       </c>
-      <c r="B100" s="159"/>
+      <c r="B100" s="155"/>
       <c r="C100" s="35" t="s">
+        <v>291</v>
+      </c>
+      <c r="D100" s="36" t="s">
         <v>292</v>
       </c>
-      <c r="D100" s="36" t="s">
-        <v>293</v>
-      </c>
-      <c r="E100" s="69" t="s">
+      <c r="E100" s="67" t="s">
+        <v>291</v>
+      </c>
+      <c r="F100" s="159" t="s">
+        <v>32</v>
+      </c>
+      <c r="G100" s="57"/>
+      <c r="H100" s="57"/>
+      <c r="I100" s="67" t="s">
         <v>292</v>
       </c>
-      <c r="F100" s="69"/>
-      <c r="G100" s="59"/>
-      <c r="H100" s="59"/>
-      <c r="I100" s="69" t="s">
-        <v>293</v>
-      </c>
-      <c r="J100" s="69" t="s">
-        <v>23</v>
-      </c>
-      <c r="K100" s="81" t="s">
-        <v>30</v>
+      <c r="J100" s="67" t="s">
+        <v>22</v>
+      </c>
+      <c r="K100" s="78" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="101" spans="1:14">
@@ -6165,27 +6278,29 @@
         <f t="shared" si="2"/>
         <v>99</v>
       </c>
-      <c r="B101" s="159"/>
-      <c r="C101" s="162" t="s">
-        <v>23</v>
+      <c r="B101" s="155"/>
+      <c r="C101" s="158" t="s">
+        <v>22</v>
       </c>
       <c r="D101" s="46" t="s">
+        <v>225</v>
+      </c>
+      <c r="E101" s="109" t="s">
         <v>226</v>
       </c>
-      <c r="E101" s="112" t="s">
-        <v>227</v>
-      </c>
-      <c r="F101" s="112"/>
-      <c r="G101" s="59"/>
-      <c r="H101" s="59"/>
-      <c r="I101" s="69" t="s">
-        <v>226</v>
-      </c>
-      <c r="J101" s="69" t="s">
-        <v>23</v>
-      </c>
-      <c r="K101" s="81" t="s">
-        <v>89</v>
+      <c r="F101" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="G101" s="57"/>
+      <c r="H101" s="57"/>
+      <c r="I101" s="67" t="s">
+        <v>225</v>
+      </c>
+      <c r="J101" s="67" t="s">
+        <v>22</v>
+      </c>
+      <c r="K101" s="78" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="102" spans="1:14">
@@ -6193,25 +6308,27 @@
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="B102" s="159"/>
-      <c r="C102" s="162"/>
+      <c r="B102" s="155"/>
+      <c r="C102" s="158"/>
       <c r="D102" s="46" t="s">
+        <v>234</v>
+      </c>
+      <c r="E102" s="65" t="s">
         <v>235</v>
       </c>
-      <c r="E102" s="67" t="s">
-        <v>236</v>
-      </c>
-      <c r="F102" s="67"/>
-      <c r="G102" s="59"/>
-      <c r="H102" s="59"/>
-      <c r="I102" s="67" t="s">
-        <v>118</v>
-      </c>
-      <c r="J102" s="67" t="s">
-        <v>23</v>
-      </c>
-      <c r="K102" s="108" t="s">
-        <v>60</v>
+      <c r="F102" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="G102" s="57"/>
+      <c r="H102" s="57"/>
+      <c r="I102" s="65" t="s">
+        <v>117</v>
+      </c>
+      <c r="J102" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="K102" s="105" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="103" spans="1:14">
@@ -6219,25 +6336,27 @@
         <f t="shared" si="2"/>
         <v>101</v>
       </c>
-      <c r="B103" s="159"/>
-      <c r="C103" s="162"/>
+      <c r="B103" s="155"/>
+      <c r="C103" s="158"/>
       <c r="D103" s="46" t="s">
+        <v>236</v>
+      </c>
+      <c r="E103" s="65" t="s">
         <v>237</v>
       </c>
-      <c r="E103" s="67" t="s">
-        <v>238</v>
-      </c>
-      <c r="F103" s="67"/>
-      <c r="G103" s="59"/>
-      <c r="H103" s="59"/>
-      <c r="I103" s="67" t="s">
-        <v>118</v>
-      </c>
-      <c r="J103" s="67" t="s">
-        <v>23</v>
-      </c>
-      <c r="K103" s="108" t="s">
-        <v>60</v>
+      <c r="F103" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="G103" s="57"/>
+      <c r="H103" s="57"/>
+      <c r="I103" s="65" t="s">
+        <v>117</v>
+      </c>
+      <c r="J103" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="K103" s="105" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="104" spans="1:14">
@@ -6245,25 +6364,27 @@
         <f t="shared" si="2"/>
         <v>102</v>
       </c>
-      <c r="B104" s="159"/>
-      <c r="C104" s="162"/>
+      <c r="B104" s="155"/>
+      <c r="C104" s="158"/>
       <c r="D104" s="46" t="s">
-        <v>239</v>
-      </c>
-      <c r="E104" s="70" t="s">
-        <v>63</v>
-      </c>
-      <c r="F104" s="70"/>
-      <c r="G104" s="59"/>
-      <c r="H104" s="59"/>
-      <c r="I104" s="70" t="s">
-        <v>63</v>
-      </c>
-      <c r="J104" s="70" t="s">
-        <v>23</v>
-      </c>
-      <c r="K104" s="108" t="s">
-        <v>60</v>
+        <v>238</v>
+      </c>
+      <c r="E104" s="68" t="s">
+        <v>62</v>
+      </c>
+      <c r="F104" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="G104" s="57"/>
+      <c r="H104" s="57"/>
+      <c r="I104" s="68" t="s">
+        <v>62</v>
+      </c>
+      <c r="J104" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="K104" s="105" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="105" spans="1:14">
@@ -6271,27 +6392,27 @@
         <f t="shared" si="2"/>
         <v>103</v>
       </c>
-      <c r="B105" s="159"/>
-      <c r="C105" s="139" t="s">
+      <c r="B105" s="155"/>
+      <c r="C105" s="135" t="s">
+        <v>293</v>
+      </c>
+      <c r="D105" s="46" t="s">
         <v>294</v>
       </c>
-      <c r="D105" s="46" t="s">
+      <c r="E105" s="108" t="s">
         <v>295</v>
       </c>
-      <c r="E105" s="111" t="s">
-        <v>296</v>
-      </c>
-      <c r="F105" s="111"/>
-      <c r="G105" s="59"/>
-      <c r="H105" s="59"/>
-      <c r="I105" s="67" t="s">
-        <v>295</v>
-      </c>
-      <c r="J105" s="67" t="s">
-        <v>23</v>
-      </c>
-      <c r="K105" s="108" t="s">
-        <v>126</v>
+      <c r="F105" s="108"/>
+      <c r="G105" s="57"/>
+      <c r="H105" s="57"/>
+      <c r="I105" s="65" t="s">
+        <v>294</v>
+      </c>
+      <c r="J105" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="K105" s="105" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="106" spans="1:14" ht="33" customHeight="1">
@@ -6299,45 +6420,49 @@
         <f t="shared" si="2"/>
         <v>104</v>
       </c>
-      <c r="B106" s="159"/>
-      <c r="C106" s="139"/>
+      <c r="B106" s="155"/>
+      <c r="C106" s="135"/>
       <c r="D106" s="42" t="s">
+        <v>296</v>
+      </c>
+      <c r="E106" s="107" t="s">
         <v>297</v>
       </c>
-      <c r="E106" s="110" t="s">
-        <v>298</v>
-      </c>
-      <c r="F106" s="110"/>
-      <c r="G106" s="116"/>
-      <c r="H106" s="116"/>
-      <c r="I106" s="122"/>
-      <c r="J106" s="122"/>
-      <c r="K106" s="123"/>
+      <c r="F106" s="159" t="s">
+        <v>32</v>
+      </c>
+      <c r="G106" s="113"/>
+      <c r="H106" s="113"/>
+      <c r="I106" s="119"/>
+      <c r="J106" s="119"/>
+      <c r="K106" s="120"/>
     </row>
     <row r="107" spans="1:14" ht="33" customHeight="1">
       <c r="A107" s="51">
         <f t="shared" si="2"/>
         <v>105</v>
       </c>
-      <c r="B107" s="159"/>
-      <c r="C107" s="139"/>
+      <c r="B107" s="155"/>
+      <c r="C107" s="135"/>
       <c r="D107" s="36" t="s">
+        <v>298</v>
+      </c>
+      <c r="E107" s="51" t="s">
         <v>299</v>
       </c>
-      <c r="E107" s="51" t="s">
-        <v>300</v>
-      </c>
-      <c r="F107" s="133"/>
-      <c r="G107" s="59"/>
-      <c r="H107" s="59"/>
+      <c r="F107" s="159" t="s">
+        <v>32</v>
+      </c>
+      <c r="G107" s="57"/>
+      <c r="H107" s="57"/>
       <c r="I107" s="51" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J107" s="51" t="s">
-        <v>23</v>
-      </c>
-      <c r="K107" s="89" t="s">
-        <v>196</v>
+        <v>22</v>
+      </c>
+      <c r="K107" s="86" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="108" spans="1:14" ht="33" customHeight="1">
@@ -6345,25 +6470,27 @@
         <f t="shared" si="2"/>
         <v>106</v>
       </c>
-      <c r="B108" s="159"/>
-      <c r="C108" s="139"/>
+      <c r="B108" s="155"/>
+      <c r="C108" s="135"/>
       <c r="D108" s="36" t="s">
+        <v>300</v>
+      </c>
+      <c r="E108" s="65" t="s">
         <v>301</v>
       </c>
-      <c r="E108" s="67" t="s">
-        <v>302</v>
-      </c>
-      <c r="F108" s="67"/>
-      <c r="G108" s="59"/>
-      <c r="H108" s="59"/>
-      <c r="I108" s="67" t="s">
-        <v>301</v>
-      </c>
-      <c r="J108" s="67" t="s">
-        <v>23</v>
-      </c>
-      <c r="K108" s="108" t="s">
-        <v>301</v>
+      <c r="F108" s="159" t="s">
+        <v>32</v>
+      </c>
+      <c r="G108" s="57"/>
+      <c r="H108" s="57"/>
+      <c r="I108" s="65" t="s">
+        <v>300</v>
+      </c>
+      <c r="J108" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="K108" s="105" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="109" spans="1:14" ht="33" customHeight="1">
@@ -6371,25 +6498,27 @@
         <f t="shared" si="2"/>
         <v>107</v>
       </c>
-      <c r="B109" s="159"/>
-      <c r="C109" s="139"/>
+      <c r="B109" s="155"/>
+      <c r="C109" s="135"/>
       <c r="D109" s="36" t="s">
+        <v>302</v>
+      </c>
+      <c r="E109" s="65" t="s">
         <v>303</v>
       </c>
-      <c r="E109" s="67" t="s">
-        <v>304</v>
-      </c>
-      <c r="F109" s="67"/>
-      <c r="G109" s="59"/>
-      <c r="H109" s="59"/>
-      <c r="I109" s="67" t="s">
-        <v>303</v>
-      </c>
-      <c r="J109" s="67" t="s">
-        <v>23</v>
-      </c>
-      <c r="K109" s="108" t="s">
-        <v>126</v>
+      <c r="F109" s="159" t="s">
+        <v>32</v>
+      </c>
+      <c r="G109" s="57"/>
+      <c r="H109" s="57"/>
+      <c r="I109" s="65" t="s">
+        <v>302</v>
+      </c>
+      <c r="J109" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="K109" s="105" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="110" spans="1:14" ht="33" customHeight="1">
@@ -6397,25 +6526,27 @@
         <f t="shared" si="2"/>
         <v>108</v>
       </c>
-      <c r="B110" s="159"/>
-      <c r="C110" s="139"/>
+      <c r="B110" s="155"/>
+      <c r="C110" s="135"/>
       <c r="D110" s="36" t="s">
+        <v>304</v>
+      </c>
+      <c r="E110" s="67" t="s">
         <v>305</v>
       </c>
-      <c r="E110" s="69" t="s">
-        <v>306</v>
-      </c>
-      <c r="F110" s="69"/>
-      <c r="G110" s="59"/>
-      <c r="H110" s="59"/>
-      <c r="I110" s="69" t="s">
-        <v>305</v>
-      </c>
-      <c r="J110" s="69" t="s">
-        <v>23</v>
-      </c>
-      <c r="K110" s="81" t="s">
-        <v>126</v>
+      <c r="F110" s="159" t="s">
+        <v>32</v>
+      </c>
+      <c r="G110" s="57"/>
+      <c r="H110" s="57"/>
+      <c r="I110" s="67" t="s">
+        <v>304</v>
+      </c>
+      <c r="J110" s="67" t="s">
+        <v>22</v>
+      </c>
+      <c r="K110" s="78" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="111" spans="1:14" ht="33" customHeight="1">
@@ -6423,25 +6554,27 @@
         <f t="shared" si="2"/>
         <v>109</v>
       </c>
-      <c r="B111" s="159"/>
-      <c r="C111" s="139"/>
+      <c r="B111" s="155"/>
+      <c r="C111" s="135"/>
       <c r="D111" s="36" t="s">
+        <v>306</v>
+      </c>
+      <c r="E111" s="67" t="s">
         <v>307</v>
       </c>
-      <c r="E111" s="69" t="s">
+      <c r="F111" s="159" t="s">
+        <v>32</v>
+      </c>
+      <c r="G111" s="57"/>
+      <c r="H111" s="57"/>
+      <c r="I111" s="67" t="s">
         <v>308</v>
       </c>
-      <c r="F111" s="69"/>
-      <c r="G111" s="59"/>
-      <c r="H111" s="59"/>
-      <c r="I111" s="69" t="s">
-        <v>309</v>
-      </c>
-      <c r="J111" s="69" t="s">
+      <c r="J111" s="67" t="s">
+        <v>22</v>
+      </c>
+      <c r="K111" s="78" t="s">
         <v>23</v>
-      </c>
-      <c r="K111" s="81" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="112" spans="1:14" ht="33" customHeight="1">
@@ -6449,25 +6582,27 @@
         <f t="shared" si="2"/>
         <v>110</v>
       </c>
-      <c r="B112" s="159"/>
-      <c r="C112" s="139"/>
+      <c r="B112" s="155"/>
+      <c r="C112" s="135"/>
       <c r="D112" s="42" t="s">
+        <v>309</v>
+      </c>
+      <c r="E112" s="67" t="s">
         <v>310</v>
       </c>
-      <c r="E112" s="69" t="s">
-        <v>311</v>
-      </c>
-      <c r="F112" s="69"/>
-      <c r="G112" s="59"/>
-      <c r="H112" s="59"/>
-      <c r="I112" s="69" t="s">
+      <c r="F112" s="159" t="s">
+        <v>32</v>
+      </c>
+      <c r="G112" s="57"/>
+      <c r="H112" s="57"/>
+      <c r="I112" s="67" t="s">
+        <v>124</v>
+      </c>
+      <c r="J112" s="67" t="s">
+        <v>22</v>
+      </c>
+      <c r="K112" s="78" t="s">
         <v>125</v>
-      </c>
-      <c r="J112" s="69" t="s">
-        <v>23</v>
-      </c>
-      <c r="K112" s="81" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="113" spans="1:11" ht="33" customHeight="1">
@@ -6475,25 +6610,27 @@
         <f t="shared" si="2"/>
         <v>111</v>
       </c>
-      <c r="B113" s="159"/>
-      <c r="C113" s="139"/>
+      <c r="B113" s="155"/>
+      <c r="C113" s="135"/>
       <c r="D113" s="47" t="s">
+        <v>311</v>
+      </c>
+      <c r="E113" s="67" t="s">
         <v>312</v>
       </c>
-      <c r="E113" s="69" t="s">
+      <c r="F113" s="159" t="s">
+        <v>32</v>
+      </c>
+      <c r="G113" s="57"/>
+      <c r="H113" s="57"/>
+      <c r="I113" s="67" t="s">
         <v>313</v>
       </c>
-      <c r="F113" s="69"/>
-      <c r="G113" s="59"/>
-      <c r="H113" s="59"/>
-      <c r="I113" s="69" t="s">
-        <v>314</v>
-      </c>
-      <c r="J113" s="69" t="s">
-        <v>23</v>
-      </c>
-      <c r="K113" s="81" t="s">
-        <v>126</v>
+      <c r="J113" s="67" t="s">
+        <v>22</v>
+      </c>
+      <c r="K113" s="78" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="114" spans="1:11">
@@ -6501,27 +6638,29 @@
         <f t="shared" si="2"/>
         <v>112</v>
       </c>
-      <c r="B114" s="159"/>
+      <c r="B114" s="155"/>
       <c r="C114" s="35" t="s">
+        <v>314</v>
+      </c>
+      <c r="D114" s="44" t="s">
         <v>315</v>
       </c>
-      <c r="D114" s="44" t="s">
+      <c r="E114" s="67" t="s">
         <v>316</v>
       </c>
-      <c r="E114" s="69" t="s">
-        <v>317</v>
-      </c>
-      <c r="F114" s="69"/>
-      <c r="G114" s="59"/>
-      <c r="H114" s="59"/>
-      <c r="I114" s="69" t="s">
-        <v>316</v>
-      </c>
-      <c r="J114" s="69" t="s">
-        <v>23</v>
-      </c>
-      <c r="K114" s="81" t="s">
-        <v>316</v>
+      <c r="F114" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G114" s="57"/>
+      <c r="H114" s="57"/>
+      <c r="I114" s="67" t="s">
+        <v>315</v>
+      </c>
+      <c r="J114" s="67" t="s">
+        <v>22</v>
+      </c>
+      <c r="K114" s="78" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="115" spans="1:11">
@@ -6529,27 +6668,29 @@
         <f t="shared" si="2"/>
         <v>113</v>
       </c>
-      <c r="B115" s="159"/>
+      <c r="B115" s="155"/>
       <c r="C115" s="35" t="s">
+        <v>317</v>
+      </c>
+      <c r="D115" s="44" t="s">
         <v>318</v>
       </c>
-      <c r="D115" s="44" t="s">
+      <c r="E115" s="67" t="s">
+        <v>317</v>
+      </c>
+      <c r="F115" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G115" s="57"/>
+      <c r="H115" s="57"/>
+      <c r="I115" s="67" t="s">
         <v>319</v>
       </c>
-      <c r="E115" s="69" t="s">
-        <v>318</v>
-      </c>
-      <c r="F115" s="69"/>
-      <c r="G115" s="59"/>
-      <c r="H115" s="59"/>
-      <c r="I115" s="69" t="s">
+      <c r="J115" s="67" t="s">
+        <v>22</v>
+      </c>
+      <c r="K115" s="78" t="s">
         <v>320</v>
-      </c>
-      <c r="J115" s="69" t="s">
-        <v>23</v>
-      </c>
-      <c r="K115" s="81" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="116" spans="1:11">
@@ -6557,27 +6698,29 @@
         <f t="shared" si="2"/>
         <v>114</v>
       </c>
-      <c r="B116" s="159"/>
-      <c r="C116" s="139" t="s">
+      <c r="B116" s="155"/>
+      <c r="C116" s="135" t="s">
+        <v>321</v>
+      </c>
+      <c r="D116" s="45" t="s">
         <v>322</v>
       </c>
-      <c r="D116" s="45" t="s">
+      <c r="E116" s="65" t="s">
         <v>323</v>
       </c>
-      <c r="E116" s="67" t="s">
-        <v>324</v>
-      </c>
-      <c r="F116" s="67"/>
-      <c r="G116" s="59"/>
-      <c r="H116" s="59"/>
-      <c r="I116" s="67" t="s">
-        <v>323</v>
-      </c>
-      <c r="J116" s="124" t="s">
-        <v>23</v>
-      </c>
-      <c r="K116" s="108" t="s">
-        <v>99</v>
+      <c r="F116" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="G116" s="57"/>
+      <c r="H116" s="57"/>
+      <c r="I116" s="65" t="s">
+        <v>322</v>
+      </c>
+      <c r="J116" s="121" t="s">
+        <v>22</v>
+      </c>
+      <c r="K116" s="105" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="117" spans="1:11">
@@ -6585,25 +6728,27 @@
         <f t="shared" si="2"/>
         <v>115</v>
       </c>
-      <c r="B117" s="159"/>
-      <c r="C117" s="139"/>
+      <c r="B117" s="155"/>
+      <c r="C117" s="135"/>
       <c r="D117" s="45" t="s">
+        <v>324</v>
+      </c>
+      <c r="E117" s="65" t="s">
         <v>325</v>
       </c>
-      <c r="E117" s="67" t="s">
-        <v>326</v>
-      </c>
-      <c r="F117" s="67"/>
-      <c r="G117" s="59"/>
-      <c r="H117" s="59"/>
-      <c r="I117" s="67" t="s">
-        <v>325</v>
-      </c>
-      <c r="J117" s="124" t="s">
-        <v>23</v>
-      </c>
-      <c r="K117" s="108" t="s">
-        <v>99</v>
+      <c r="F117" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="G117" s="57"/>
+      <c r="H117" s="57"/>
+      <c r="I117" s="65" t="s">
+        <v>324</v>
+      </c>
+      <c r="J117" s="121" t="s">
+        <v>22</v>
+      </c>
+      <c r="K117" s="105" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="118" spans="1:11">
@@ -6611,25 +6756,27 @@
         <f t="shared" si="2"/>
         <v>116</v>
       </c>
-      <c r="B118" s="159"/>
-      <c r="C118" s="139"/>
+      <c r="B118" s="155"/>
+      <c r="C118" s="135"/>
       <c r="D118" s="45" t="s">
+        <v>326</v>
+      </c>
+      <c r="E118" s="65" t="s">
         <v>327</v>
       </c>
-      <c r="E118" s="67" t="s">
-        <v>328</v>
-      </c>
-      <c r="F118" s="67"/>
-      <c r="G118" s="59"/>
-      <c r="H118" s="59"/>
-      <c r="I118" s="67" t="s">
-        <v>327</v>
-      </c>
-      <c r="J118" s="124" t="s">
-        <v>23</v>
-      </c>
-      <c r="K118" s="108" t="s">
-        <v>99</v>
+      <c r="F118" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="G118" s="57"/>
+      <c r="H118" s="57"/>
+      <c r="I118" s="65" t="s">
+        <v>326</v>
+      </c>
+      <c r="J118" s="121" t="s">
+        <v>22</v>
+      </c>
+      <c r="K118" s="105" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="119" spans="1:11">
@@ -6637,25 +6784,27 @@
         <f t="shared" si="2"/>
         <v>117</v>
       </c>
-      <c r="B119" s="159"/>
-      <c r="C119" s="139"/>
+      <c r="B119" s="155"/>
+      <c r="C119" s="135"/>
       <c r="D119" s="45" t="s">
+        <v>328</v>
+      </c>
+      <c r="E119" s="65" t="s">
         <v>329</v>
       </c>
-      <c r="E119" s="67" t="s">
+      <c r="F119" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="G119" s="57"/>
+      <c r="H119" s="57"/>
+      <c r="I119" s="65" t="s">
         <v>330</v>
       </c>
-      <c r="F119" s="67"/>
-      <c r="G119" s="59"/>
-      <c r="H119" s="59"/>
-      <c r="I119" s="67" t="s">
-        <v>331</v>
-      </c>
-      <c r="J119" s="124" t="s">
-        <v>23</v>
-      </c>
-      <c r="K119" s="108" t="s">
-        <v>99</v>
+      <c r="J119" s="121" t="s">
+        <v>22</v>
+      </c>
+      <c r="K119" s="105" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="120" spans="1:11">
@@ -6663,25 +6812,27 @@
         <f t="shared" si="2"/>
         <v>118</v>
       </c>
-      <c r="B120" s="159"/>
-      <c r="C120" s="139"/>
+      <c r="B120" s="155"/>
+      <c r="C120" s="135"/>
       <c r="D120" s="45" t="s">
+        <v>331</v>
+      </c>
+      <c r="E120" s="65" t="s">
         <v>332</v>
       </c>
-      <c r="E120" s="67" t="s">
-        <v>333</v>
-      </c>
-      <c r="F120" s="67"/>
-      <c r="G120" s="59"/>
-      <c r="H120" s="59"/>
-      <c r="I120" s="67" t="s">
-        <v>332</v>
-      </c>
-      <c r="J120" s="124" t="s">
-        <v>23</v>
-      </c>
-      <c r="K120" s="108" t="s">
-        <v>99</v>
+      <c r="F120" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="G120" s="57"/>
+      <c r="H120" s="57"/>
+      <c r="I120" s="65" t="s">
+        <v>331</v>
+      </c>
+      <c r="J120" s="121" t="s">
+        <v>22</v>
+      </c>
+      <c r="K120" s="105" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="121" spans="1:11">
@@ -6689,25 +6840,27 @@
         <f t="shared" si="2"/>
         <v>119</v>
       </c>
-      <c r="B121" s="159"/>
-      <c r="C121" s="139"/>
+      <c r="B121" s="155"/>
+      <c r="C121" s="135"/>
       <c r="D121" s="45" t="s">
+        <v>333</v>
+      </c>
+      <c r="E121" s="65" t="s">
         <v>334</v>
       </c>
-      <c r="E121" s="67" t="s">
-        <v>335</v>
-      </c>
-      <c r="F121" s="67"/>
-      <c r="G121" s="59"/>
-      <c r="H121" s="59"/>
-      <c r="I121" s="67" t="s">
-        <v>334</v>
-      </c>
-      <c r="J121" s="124" t="s">
-        <v>23</v>
-      </c>
-      <c r="K121" s="108" t="s">
-        <v>99</v>
+      <c r="F121" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="G121" s="57"/>
+      <c r="H121" s="57"/>
+      <c r="I121" s="65" t="s">
+        <v>333</v>
+      </c>
+      <c r="J121" s="121" t="s">
+        <v>22</v>
+      </c>
+      <c r="K121" s="105" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="122" spans="1:11">
@@ -6715,25 +6868,27 @@
         <f t="shared" si="2"/>
         <v>120</v>
       </c>
-      <c r="B122" s="159"/>
-      <c r="C122" s="139"/>
+      <c r="B122" s="155"/>
+      <c r="C122" s="135"/>
       <c r="D122" s="45" t="s">
+        <v>335</v>
+      </c>
+      <c r="E122" s="65" t="s">
         <v>336</v>
       </c>
-      <c r="E122" s="67" t="s">
+      <c r="F122" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="G122" s="57"/>
+      <c r="H122" s="57"/>
+      <c r="I122" s="65" t="s">
         <v>337</v>
       </c>
-      <c r="F122" s="67"/>
-      <c r="G122" s="59"/>
-      <c r="H122" s="59"/>
-      <c r="I122" s="67" t="s">
-        <v>338</v>
-      </c>
-      <c r="J122" s="67" t="s">
-        <v>23</v>
-      </c>
-      <c r="K122" s="108" t="s">
-        <v>99</v>
+      <c r="J122" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="K122" s="105" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="123" spans="1:11">
@@ -6741,25 +6896,27 @@
         <f t="shared" si="2"/>
         <v>121</v>
       </c>
-      <c r="B123" s="159"/>
-      <c r="C123" s="139"/>
+      <c r="B123" s="155"/>
+      <c r="C123" s="135"/>
       <c r="D123" s="45" t="s">
+        <v>338</v>
+      </c>
+      <c r="E123" s="65" t="s">
         <v>339</v>
       </c>
-      <c r="E123" s="67" t="s">
+      <c r="F123" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="G123" s="57"/>
+      <c r="H123" s="57"/>
+      <c r="I123" s="65" t="s">
         <v>340</v>
       </c>
-      <c r="F123" s="67"/>
-      <c r="G123" s="59"/>
-      <c r="H123" s="59"/>
-      <c r="I123" s="67" t="s">
-        <v>341</v>
-      </c>
-      <c r="J123" s="67" t="s">
-        <v>23</v>
-      </c>
-      <c r="K123" s="108" t="s">
-        <v>99</v>
+      <c r="J123" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="K123" s="105" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="124" spans="1:11">
@@ -6767,25 +6924,27 @@
         <f t="shared" si="2"/>
         <v>122</v>
       </c>
-      <c r="B124" s="159"/>
-      <c r="C124" s="139"/>
+      <c r="B124" s="155"/>
+      <c r="C124" s="135"/>
       <c r="D124" s="45" t="s">
+        <v>341</v>
+      </c>
+      <c r="E124" s="65" t="s">
         <v>342</v>
       </c>
-      <c r="E124" s="67" t="s">
+      <c r="F124" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="G124" s="57"/>
+      <c r="H124" s="57"/>
+      <c r="I124" s="65" t="s">
         <v>343</v>
       </c>
-      <c r="F124" s="67"/>
-      <c r="G124" s="59"/>
-      <c r="H124" s="59"/>
-      <c r="I124" s="67" t="s">
-        <v>344</v>
-      </c>
-      <c r="J124" s="67" t="s">
-        <v>23</v>
-      </c>
-      <c r="K124" s="108" t="s">
-        <v>99</v>
+      <c r="J124" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="K124" s="105" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="125" spans="1:11">
@@ -6793,25 +6952,27 @@
         <f t="shared" si="2"/>
         <v>123</v>
       </c>
-      <c r="B125" s="159"/>
-      <c r="C125" s="139"/>
+      <c r="B125" s="155"/>
+      <c r="C125" s="135"/>
       <c r="D125" s="45" t="s">
-        <v>345</v>
-      </c>
-      <c r="E125" s="67" t="s">
-        <v>35</v>
-      </c>
-      <c r="F125" s="67"/>
-      <c r="G125" s="59"/>
-      <c r="H125" s="59"/>
-      <c r="I125" s="67" t="s">
-        <v>345</v>
-      </c>
-      <c r="J125" s="67" t="s">
-        <v>23</v>
-      </c>
-      <c r="K125" s="108" t="s">
-        <v>99</v>
+        <v>344</v>
+      </c>
+      <c r="E125" s="65" t="s">
+        <v>34</v>
+      </c>
+      <c r="F125" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="G125" s="57"/>
+      <c r="H125" s="57"/>
+      <c r="I125" s="65" t="s">
+        <v>344</v>
+      </c>
+      <c r="J125" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="K125" s="105" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="126" spans="1:11">
@@ -6819,25 +6980,27 @@
         <f t="shared" si="2"/>
         <v>124</v>
       </c>
-      <c r="B126" s="159"/>
-      <c r="C126" s="139"/>
+      <c r="B126" s="155"/>
+      <c r="C126" s="135"/>
       <c r="D126" s="45" t="s">
+        <v>345</v>
+      </c>
+      <c r="E126" s="65" t="s">
         <v>346</v>
       </c>
-      <c r="E126" s="67" t="s">
+      <c r="F126" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="G126" s="57"/>
+      <c r="H126" s="57"/>
+      <c r="I126" s="65" t="s">
+        <v>345</v>
+      </c>
+      <c r="J126" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="K126" s="105" t="s">
         <v>347</v>
-      </c>
-      <c r="F126" s="67"/>
-      <c r="G126" s="59"/>
-      <c r="H126" s="59"/>
-      <c r="I126" s="67" t="s">
-        <v>346</v>
-      </c>
-      <c r="J126" s="67" t="s">
-        <v>23</v>
-      </c>
-      <c r="K126" s="108" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="127" spans="1:11">
@@ -6845,25 +7008,27 @@
         <f t="shared" si="2"/>
         <v>125</v>
       </c>
-      <c r="B127" s="159"/>
-      <c r="C127" s="139"/>
+      <c r="B127" s="155"/>
+      <c r="C127" s="135"/>
       <c r="D127" s="45" t="s">
+        <v>348</v>
+      </c>
+      <c r="E127" s="65" t="s">
         <v>349</v>
       </c>
-      <c r="E127" s="67" t="s">
-        <v>350</v>
-      </c>
-      <c r="F127" s="67"/>
-      <c r="G127" s="59"/>
-      <c r="H127" s="59"/>
-      <c r="I127" s="67" t="s">
-        <v>349</v>
-      </c>
-      <c r="J127" s="67" t="s">
+      <c r="F127" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="G127" s="57"/>
+      <c r="H127" s="57"/>
+      <c r="I127" s="65" t="s">
+        <v>348</v>
+      </c>
+      <c r="J127" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="K127" s="105" t="s">
         <v>23</v>
-      </c>
-      <c r="K127" s="108" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="128" spans="1:11">
@@ -6871,25 +7036,27 @@
         <f t="shared" si="2"/>
         <v>126</v>
       </c>
-      <c r="B128" s="159"/>
-      <c r="C128" s="139"/>
+      <c r="B128" s="155"/>
+      <c r="C128" s="135"/>
       <c r="D128" s="45" t="s">
+        <v>350</v>
+      </c>
+      <c r="E128" s="65" t="s">
         <v>351</v>
       </c>
-      <c r="E128" s="67" t="s">
-        <v>352</v>
-      </c>
-      <c r="F128" s="67"/>
-      <c r="G128" s="59"/>
-      <c r="H128" s="59"/>
-      <c r="I128" s="67" t="s">
-        <v>351</v>
-      </c>
-      <c r="J128" s="67" t="s">
+      <c r="F128" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="G128" s="57"/>
+      <c r="H128" s="57"/>
+      <c r="I128" s="65" t="s">
+        <v>350</v>
+      </c>
+      <c r="J128" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="K128" s="105" t="s">
         <v>23</v>
-      </c>
-      <c r="K128" s="108" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="129" spans="1:14">
@@ -6897,25 +7064,27 @@
         <f t="shared" si="2"/>
         <v>127</v>
       </c>
-      <c r="B129" s="159"/>
-      <c r="C129" s="139"/>
+      <c r="B129" s="155"/>
+      <c r="C129" s="135"/>
       <c r="D129" s="45" t="s">
+        <v>352</v>
+      </c>
+      <c r="E129" s="65" t="s">
         <v>353</v>
       </c>
-      <c r="E129" s="67" t="s">
-        <v>354</v>
-      </c>
-      <c r="F129" s="67"/>
-      <c r="G129" s="59"/>
-      <c r="H129" s="59"/>
-      <c r="I129" s="67" t="s">
-        <v>353</v>
-      </c>
-      <c r="J129" s="67" t="s">
-        <v>23</v>
-      </c>
-      <c r="K129" s="108" t="s">
-        <v>99</v>
+      <c r="F129" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="G129" s="57"/>
+      <c r="H129" s="57"/>
+      <c r="I129" s="65" t="s">
+        <v>352</v>
+      </c>
+      <c r="J129" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="K129" s="105" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="130" spans="1:14">
@@ -6923,25 +7092,27 @@
         <f t="shared" si="2"/>
         <v>128</v>
       </c>
-      <c r="B130" s="159"/>
-      <c r="C130" s="139"/>
+      <c r="B130" s="155"/>
+      <c r="C130" s="135"/>
       <c r="D130" s="45" t="s">
+        <v>354</v>
+      </c>
+      <c r="E130" s="65" t="s">
         <v>355</v>
       </c>
-      <c r="E130" s="67" t="s">
-        <v>356</v>
-      </c>
-      <c r="F130" s="67"/>
-      <c r="G130" s="59"/>
-      <c r="H130" s="59"/>
-      <c r="I130" s="67" t="s">
-        <v>355</v>
-      </c>
-      <c r="J130" s="67" t="s">
-        <v>23</v>
-      </c>
-      <c r="K130" s="108" t="s">
-        <v>99</v>
+      <c r="F130" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="G130" s="57"/>
+      <c r="H130" s="57"/>
+      <c r="I130" s="65" t="s">
+        <v>354</v>
+      </c>
+      <c r="J130" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="K130" s="105" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="131" spans="1:14">
@@ -6949,25 +7120,27 @@
         <f t="shared" si="2"/>
         <v>129</v>
       </c>
-      <c r="B131" s="159"/>
-      <c r="C131" s="139"/>
+      <c r="B131" s="155"/>
+      <c r="C131" s="135"/>
       <c r="D131" s="45" t="s">
+        <v>356</v>
+      </c>
+      <c r="E131" s="65" t="s">
         <v>357</v>
       </c>
-      <c r="E131" s="67" t="s">
+      <c r="F131" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="G131" s="57"/>
+      <c r="H131" s="57"/>
+      <c r="I131" s="125" t="s">
         <v>358</v>
       </c>
-      <c r="F131" s="67"/>
-      <c r="G131" s="59"/>
-      <c r="H131" s="59"/>
-      <c r="I131" s="128" t="s">
-        <v>359</v>
-      </c>
-      <c r="J131" s="128" t="s">
+      <c r="J131" s="125" t="s">
+        <v>22</v>
+      </c>
+      <c r="K131" s="126" t="s">
         <v>23</v>
-      </c>
-      <c r="K131" s="129" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="132" spans="1:14">
@@ -6975,25 +7148,27 @@
         <f t="shared" si="2"/>
         <v>130</v>
       </c>
-      <c r="B132" s="159"/>
-      <c r="C132" s="139"/>
+      <c r="B132" s="155"/>
+      <c r="C132" s="135"/>
       <c r="D132" s="45" t="s">
+        <v>359</v>
+      </c>
+      <c r="E132" s="65" t="s">
         <v>360</v>
       </c>
-      <c r="E132" s="67" t="s">
-        <v>361</v>
-      </c>
-      <c r="F132" s="67"/>
-      <c r="G132" s="59"/>
-      <c r="H132" s="127"/>
-      <c r="I132" s="126" t="s">
-        <v>359</v>
-      </c>
-      <c r="J132" s="126" t="s">
+      <c r="F132" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="G132" s="57"/>
+      <c r="H132" s="124"/>
+      <c r="I132" s="123" t="s">
+        <v>358</v>
+      </c>
+      <c r="J132" s="123" t="s">
+        <v>22</v>
+      </c>
+      <c r="K132" s="123" t="s">
         <v>23</v>
-      </c>
-      <c r="K132" s="126" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="133" spans="1:14">
@@ -7001,25 +7176,27 @@
         <f t="shared" si="2"/>
         <v>131</v>
       </c>
-      <c r="B133" s="159"/>
-      <c r="C133" s="139"/>
+      <c r="B133" s="155"/>
+      <c r="C133" s="135"/>
       <c r="D133" s="45" t="s">
+        <v>361</v>
+      </c>
+      <c r="E133" s="65" t="s">
         <v>362</v>
       </c>
-      <c r="E133" s="67" t="s">
-        <v>363</v>
-      </c>
-      <c r="F133" s="67"/>
-      <c r="G133" s="66"/>
-      <c r="H133" s="66"/>
-      <c r="I133" s="76" t="s">
-        <v>118</v>
-      </c>
-      <c r="J133" s="76" t="s">
-        <v>23</v>
-      </c>
-      <c r="K133" s="103" t="s">
-        <v>60</v>
+      <c r="F133" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="G133" s="64"/>
+      <c r="H133" s="64"/>
+      <c r="I133" s="74" t="s">
+        <v>117</v>
+      </c>
+      <c r="J133" s="74" t="s">
+        <v>22</v>
+      </c>
+      <c r="K133" s="100" t="s">
+        <v>59</v>
       </c>
       <c r="L133" s="54"/>
     </row>
@@ -7028,25 +7205,27 @@
         <f t="shared" si="2"/>
         <v>132</v>
       </c>
-      <c r="B134" s="159"/>
-      <c r="C134" s="139"/>
+      <c r="B134" s="155"/>
+      <c r="C134" s="135"/>
       <c r="D134" s="45" t="s">
-        <v>364</v>
-      </c>
-      <c r="E134" s="69" t="s">
-        <v>238</v>
-      </c>
-      <c r="F134" s="69"/>
-      <c r="G134" s="59"/>
-      <c r="H134" s="59"/>
-      <c r="I134" s="125" t="s">
-        <v>118</v>
-      </c>
-      <c r="J134" s="125" t="s">
-        <v>23</v>
-      </c>
-      <c r="K134" s="81" t="s">
-        <v>60</v>
+        <v>363</v>
+      </c>
+      <c r="E134" s="67" t="s">
+        <v>237</v>
+      </c>
+      <c r="F134" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="G134" s="57"/>
+      <c r="H134" s="57"/>
+      <c r="I134" s="122" t="s">
+        <v>117</v>
+      </c>
+      <c r="J134" s="122" t="s">
+        <v>22</v>
+      </c>
+      <c r="K134" s="78" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="135" spans="1:14">
@@ -7054,202 +7233,192 @@
         <f t="shared" si="2"/>
         <v>133</v>
       </c>
-      <c r="B135" s="160"/>
-      <c r="C135" s="61" t="s">
+      <c r="B135" s="156"/>
+      <c r="C135" s="59" t="s">
+        <v>364</v>
+      </c>
+      <c r="D135" s="60" t="s">
         <v>365</v>
       </c>
-      <c r="D135" s="62" t="s">
+      <c r="E135" s="69" t="s">
         <v>366</v>
       </c>
-      <c r="E135" s="71" t="s">
+      <c r="F135" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G135" s="75"/>
+      <c r="H135" s="75"/>
+      <c r="I135" s="65" t="s">
         <v>367</v>
       </c>
-      <c r="F135" s="71"/>
-      <c r="G135" s="78"/>
-      <c r="H135" s="78"/>
-      <c r="I135" s="67" t="s">
+      <c r="J135" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="K135" s="105" t="s">
         <v>368</v>
       </c>
-      <c r="J135" s="67" t="s">
-        <v>23</v>
-      </c>
-      <c r="K135" s="108" t="s">
+    </row>
+    <row r="136" spans="1:14" ht="85.5">
+      <c r="A136" s="56">
+        <v>1</v>
+      </c>
+      <c r="B136" s="143" t="s">
         <v>369</v>
       </c>
-    </row>
-    <row r="136" spans="1:14">
-      <c r="A136" s="56" t="s">
+      <c r="C136" s="147" t="s">
+        <v>192</v>
+      </c>
+      <c r="D136" s="61" t="s">
+        <v>370</v>
+      </c>
+      <c r="E136" s="110" t="s">
+        <v>371</v>
+      </c>
+      <c r="F136" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G136" s="62" t="s">
+        <v>372</v>
+      </c>
+      <c r="H136" s="63"/>
+      <c r="I136" s="76"/>
+      <c r="J136" s="77"/>
+      <c r="K136" s="77"/>
+      <c r="L136" s="55"/>
+      <c r="N136"/>
+    </row>
+    <row r="137" spans="1:14">
+      <c r="A137" s="51">
+        <f>A136+1</f>
         <v>2</v>
       </c>
-      <c r="B136" s="57" t="s">
-        <v>3</v>
-      </c>
-      <c r="C136" s="57" t="s">
-        <v>4</v>
-      </c>
-      <c r="D136" s="57" t="s">
-        <v>370</v>
-      </c>
-      <c r="E136" s="57" t="s">
-        <v>371</v>
-      </c>
-      <c r="F136" s="57"/>
-      <c r="G136" s="57" t="s">
-        <v>7</v>
-      </c>
-      <c r="H136" s="57" t="s">
-        <v>8</v>
-      </c>
-      <c r="I136" s="57"/>
-      <c r="J136" s="57"/>
-      <c r="K136" s="77"/>
-    </row>
-    <row r="137" spans="1:14" ht="85.5">
-      <c r="A137" s="58">
-        <v>1</v>
-      </c>
-      <c r="B137" s="147" t="s">
-        <v>372</v>
-      </c>
-      <c r="C137" s="151" t="s">
-        <v>193</v>
-      </c>
-      <c r="D137" s="63" t="s">
+      <c r="B137" s="149"/>
+      <c r="C137" s="148"/>
+      <c r="D137" s="45" t="s">
         <v>373</v>
       </c>
-      <c r="E137" s="113" t="s">
+      <c r="E137" s="111" t="s">
         <v>374</v>
       </c>
-      <c r="F137" s="113"/>
-      <c r="G137" s="64" t="s">
+      <c r="F137" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="G137" s="58" t="s">
         <v>375</v>
       </c>
-      <c r="H137" s="65"/>
-      <c r="I137" s="79"/>
-      <c r="J137" s="80"/>
-      <c r="K137" s="80"/>
+      <c r="H137" s="35"/>
+      <c r="I137" s="78"/>
+      <c r="J137" s="79"/>
+      <c r="K137" s="79"/>
       <c r="L137" s="55"/>
-      <c r="N137"/>
-    </row>
-    <row r="138" spans="1:14">
+    </row>
+    <row r="138" spans="1:14" ht="15.75">
       <c r="A138" s="51">
         <f>A137+1</f>
-        <v>2</v>
-      </c>
-      <c r="B138" s="153"/>
-      <c r="C138" s="152"/>
-      <c r="D138" s="45" t="s">
+        <v>3</v>
+      </c>
+      <c r="B138" s="149"/>
+      <c r="C138" s="52" t="s">
         <v>376</v>
       </c>
-      <c r="E138" s="114" t="s">
+      <c r="D138" s="48" t="s">
         <v>377</v>
       </c>
-      <c r="F138" s="114"/>
-      <c r="G138" s="60" t="s">
+      <c r="E138" s="111" t="s">
         <v>378</v>
       </c>
+      <c r="F138" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="G138" s="58" t="s">
+        <v>375</v>
+      </c>
       <c r="H138" s="35"/>
-      <c r="I138" s="81"/>
-      <c r="J138" s="82"/>
-      <c r="K138" s="82"/>
+      <c r="I138" s="78"/>
+      <c r="J138" s="79"/>
+      <c r="K138" s="79"/>
       <c r="L138" s="55"/>
     </row>
-    <row r="139" spans="1:14" ht="15.75">
+    <row r="139" spans="1:14">
       <c r="A139" s="51">
-        <f>A138+1</f>
-        <v>3</v>
-      </c>
-      <c r="B139" s="153"/>
-      <c r="C139" s="52" t="s">
+        <f t="shared" ref="A139:A141" si="3">A138+1</f>
+        <v>4</v>
+      </c>
+      <c r="B139" s="149"/>
+      <c r="C139" s="127" t="s">
+        <v>22</v>
+      </c>
+      <c r="D139" s="49" t="s">
         <v>379</v>
       </c>
-      <c r="D139" s="48" t="s">
+      <c r="E139" s="111" t="s">
         <v>380</v>
       </c>
-      <c r="E139" s="114" t="s">
-        <v>381</v>
-      </c>
-      <c r="F139" s="114"/>
-      <c r="G139" s="60" t="s">
-        <v>378</v>
+      <c r="F139" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="G139" s="58" t="s">
+        <v>375</v>
       </c>
       <c r="H139" s="35"/>
-      <c r="I139" s="81"/>
-      <c r="J139" s="82"/>
-      <c r="K139" s="82"/>
+      <c r="I139" s="78"/>
+      <c r="J139" s="79"/>
+      <c r="K139" s="79"/>
       <c r="L139" s="55"/>
     </row>
     <row r="140" spans="1:14">
       <c r="A140" s="51">
-        <f t="shared" ref="A140:A142" si="3">A139+1</f>
-        <v>4</v>
-      </c>
-      <c r="B140" s="153"/>
-      <c r="C140" s="130" t="s">
-        <v>23</v>
-      </c>
-      <c r="D140" s="49" t="s">
-        <v>382</v>
-      </c>
-      <c r="E140" s="114" t="s">
-        <v>383</v>
-      </c>
-      <c r="F140" s="114"/>
-      <c r="G140" s="60" t="s">
-        <v>378</v>
-      </c>
-      <c r="H140" s="35"/>
-      <c r="I140" s="81"/>
-      <c r="J140" s="82"/>
-      <c r="K140" s="82"/>
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="B140" s="149"/>
+      <c r="C140" s="128"/>
+      <c r="D140" s="70" t="s">
+        <v>125</v>
+      </c>
+      <c r="E140" s="112" t="s">
+        <v>381</v>
+      </c>
+      <c r="F140" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="G140" s="71" t="s">
+        <v>375</v>
+      </c>
+      <c r="H140" s="59"/>
+      <c r="I140" s="80"/>
+      <c r="J140" s="81"/>
+      <c r="K140" s="81"/>
       <c r="L140" s="55"/>
     </row>
-    <row r="141" spans="1:14">
+    <row r="141" spans="1:14" ht="42.75">
       <c r="A141" s="51">
         <f t="shared" si="3"/>
-        <v>5</v>
-      </c>
-      <c r="B141" s="153"/>
-      <c r="C141" s="131"/>
-      <c r="D141" s="72" t="s">
-        <v>126</v>
-      </c>
-      <c r="E141" s="115" t="s">
+        <v>6</v>
+      </c>
+      <c r="B141" s="150"/>
+      <c r="C141" s="129" t="s">
+        <v>321</v>
+      </c>
+      <c r="D141" s="45" t="s">
+        <v>382</v>
+      </c>
+      <c r="E141" s="111" t="s">
+        <v>383</v>
+      </c>
+      <c r="F141" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="G141" s="53" t="s">
         <v>384</v>
       </c>
-      <c r="F141" s="115"/>
-      <c r="G141" s="73" t="s">
-        <v>378</v>
-      </c>
-      <c r="H141" s="61"/>
-      <c r="I141" s="83"/>
-      <c r="J141" s="84"/>
-      <c r="K141" s="84"/>
-      <c r="L141" s="55"/>
-    </row>
-    <row r="142" spans="1:14" ht="42.75">
-      <c r="A142" s="51">
-        <f t="shared" si="3"/>
-        <v>6</v>
-      </c>
-      <c r="B142" s="154"/>
-      <c r="C142" s="132" t="s">
-        <v>322</v>
-      </c>
-      <c r="D142" s="45" t="s">
-        <v>385</v>
-      </c>
-      <c r="E142" s="114" t="s">
-        <v>386</v>
-      </c>
-      <c r="F142" s="114"/>
-      <c r="G142" s="53" t="s">
-        <v>387</v>
-      </c>
-      <c r="H142" s="75"/>
-      <c r="I142" s="81"/>
-      <c r="J142" s="82"/>
-      <c r="K142" s="82"/>
+      <c r="H141" s="73"/>
+      <c r="I141" s="78"/>
+      <c r="J141" s="79"/>
+      <c r="K141" s="79"/>
+    </row>
+    <row r="142" spans="1:14">
+      <c r="B142" s="24"/>
     </row>
     <row r="143" spans="1:14">
       <c r="B143" s="24"/>
@@ -7524,12 +7693,9 @@
     <row r="233" spans="2:2">
       <c r="B233" s="24"/>
     </row>
-    <row r="234" spans="2:2">
-      <c r="B234" s="24"/>
-    </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="B137:B142"/>
+    <mergeCell ref="B136:B141"/>
     <mergeCell ref="B3:B38"/>
     <mergeCell ref="C29:C38"/>
     <mergeCell ref="B39:B135"/>
@@ -7547,7 +7713,7 @@
     <mergeCell ref="C71:C79"/>
     <mergeCell ref="C61:C70"/>
     <mergeCell ref="L14:L37"/>
-    <mergeCell ref="C137:C138"/>
+    <mergeCell ref="C136:C137"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="C49:C55"/>
